--- a/results/job_matches_2026-07-15.xlsx
+++ b/results/job_matches_2026-07-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,25 +888,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Azure Data Architect (remote US)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Winfo Solutions</t>
+          <t>News Corp</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1691b4d7b52de9</t>
+          <t>https://www.indeed.com/viewjob?jk=d584a94be46cf8b0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Azure Data Architect (remote US)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>News Corp</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d584a94be46cf8b0</t>
+          <t>https://www.indeed.com/viewjob?jk=3720530c1ac33814</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Glue/Python/Pyspark</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3720530c1ac33814</t>
+          <t>https://www.indeed.com/viewjob?jk=0bd064010356a824</t>
         </is>
       </c>
     </row>
@@ -1588,52 +1588,52 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Cloud Ops Engineer I - SRE</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CaseWorthy</t>
+          <t>Ideas2IT Technology Services</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tennyson, IN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d69f297c014e4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=3c514f50b938a8dc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Senior Cloud Ops Engineer I - SRE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Escalent</t>
+          <t>CaseWorthy</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45d62ba2dc0bd875</t>
+          <t>https://www.indeed.com/viewjob?jk=9d69f297c014e4a1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer - Front-End Focused</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>STAND TOGETHER</t>
+          <t>Escalent</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3221281fdf023197</t>
+          <t>https://www.indeed.com/viewjob?jk=45d62ba2dc0bd875</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Development Engineer I - ArcGIS Enterprise</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b08010c09c91435</t>
+          <t>https://www.indeed.com/viewjob?jk=7481c6f102626c6e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Full-Stack Software Engineer - Front-End Focused</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>STAND TOGETHER</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69cd7125f7a833</t>
+          <t>https://www.indeed.com/viewjob?jk=3221281fdf023197</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c09787e1cb8cb395</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69cd7125f7a833</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4ad7ea1b58a31e</t>
+          <t>https://www.indeed.com/viewjob?jk=c09787e1cb8cb395</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc726639aa959a6</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4ad7ea1b58a31e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Spark Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cb65007f4e4e07a</t>
+          <t>https://www.indeed.com/viewjob?jk=1cc726639aa959a6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Spark Engineer</t>
+          <t>Software Development Engineer I - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7beab78b75a48b8</t>
+          <t>https://www.indeed.com/viewjob?jk=0b08010c09c91435</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Engineer</t>
+          <t>Spark Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c44bbcac30a87c2</t>
+          <t>https://www.indeed.com/viewjob?jk=2cb65007f4e4e07a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Engineer</t>
+          <t>Spark Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc37b1c10548573</t>
+          <t>https://www.indeed.com/viewjob?jk=e7beab78b75a48b8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Scala, ETL, Tableau, Terraform, Docker, Airflow</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221a044944e1b41d</t>
+          <t>https://www.indeed.com/viewjob?jk=0c44bbcac30a87c2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Senior AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,19 +2106,19 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decf563d2df9d00c</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc37b1c10548573</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, YARN, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, Athena, Scala, ETL, Tableau, Terraform, Docker, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52c472962c791de2</t>
+          <t>https://www.indeed.com/viewjob?jk=221a044944e1b41d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Advanced Software Engineer- Full Stack Cloud Developer</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78950b770ed7417f</t>
+          <t>https://www.indeed.com/viewjob?jk=decf563d2df9d00c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sigma Report Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>El Toro.com</t>
+          <t>Tachyon Technologies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42d84e2b583adb0</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8d0798b16bd29a</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sigma Report Developer</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tachyon Technologies</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Azure, Blob Storage, YARN, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8d0798b16bd29a</t>
+          <t>https://www.indeed.com/viewjob?jk=52c472962c791de2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Platform Engineer (Hybrid)</t>
+          <t>Advanced Software Engineer- Full Stack Cloud Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, Snowflake, DynamoDB, ELT, Splunk, MLflow</t>
+          <t>AWS, S3, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a8050d86dd2bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=78950b770ed7417f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Quality and Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>El Toro.com</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Vance, AL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a36a0ff08797a70</t>
+          <t>https://www.indeed.com/viewjob?jk=d42d84e2b583adb0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Quality and Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Mercedes-Benz Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Vance, AL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36c700922532ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=3a36a0ff08797a70</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d19f755ee8489a</t>
+          <t>https://www.indeed.com/viewjob?jk=be21268d9d981efd</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, PySpark, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4223c8030b51f20b</t>
+          <t>https://www.indeed.com/viewjob?jk=f756de42016efc57</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-2027 Information Technology - Software Engineer - Intern</t>
+          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab14599c79da82b</t>
+          <t>https://www.indeed.com/viewjob?jk=abc756e24b7ebb78</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-2027 Information Technology - Software Engineer - Full-Time</t>
+          <t>Senior Snowflake Data Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
+          <t>AWS, Redshift, S3, RDS, Scala, Snowflake, DynamoDB, ELT, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6578ea1eb5e5142</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a8050d86dd2bf8</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer- Hybrid</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936d9e38993af00c</t>
+          <t>https://www.indeed.com/viewjob?jk=b36c700922532ac2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Azure Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf57c7d8b4b2d9e4</t>
+          <t>https://www.indeed.com/viewjob?jk=32d19f755ee8489a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full Stack Developer III - Private Markets Applications</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, PySpark, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f2e93224c9a790</t>
+          <t>https://www.indeed.com/viewjob?jk=4223c8030b51f20b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>2026-2027 Information Technology - Software Engineer - Intern</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032b8db4bfd5e6d8</t>
+          <t>https://www.indeed.com/viewjob?jk=eab14599c79da82b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>2026-2027 Information Technology - Software Engineer - Full-Time</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f856d080d24d05</t>
+          <t>https://www.indeed.com/viewjob?jk=d6578ea1eb5e5142</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Data Engineer- Hybrid</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Match Made Tech</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19153bb3202f8519</t>
+          <t>https://www.indeed.com/viewjob?jk=936d9e38993af00c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior .NET and SSRS Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee7a2d23cf0b0fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c8883b0dd19abf</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Full Stack Developer III - Private Markets Applications</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3e62df8c707d8</t>
+          <t>https://www.indeed.com/viewjob?jk=04f2e93224c9a790</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=779a1a0a5eccc32e</t>
+          <t>https://www.indeed.com/viewjob?jk=bf57c7d8b4b2d9e4</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8993a2c0de0e70e1</t>
+          <t>https://www.indeed.com/viewjob?jk=032b8db4bfd5e6d8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>RPA Engineer</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+          <t>https://www.indeed.com/viewjob?jk=46f856d080d24d05</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior .NET and SSRS Developer</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c8883b0dd19abf</t>
+          <t>https://www.indeed.com/viewjob?jk=19153bb3202f8519</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,15 +2963,15 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, DataOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ebbf24573d559b5</t>
+          <t>https://www.indeed.com/viewjob?jk=ee7a2d23cf0b0fbe</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Product</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Re:Build Manufacturing</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,129 +3016,129 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d08f5c56b39289</t>
+          <t>https://www.indeed.com/viewjob?jk=00a3e62df8c707d8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb8dc7b4cca4c33</t>
+          <t>https://www.indeed.com/viewjob?jk=779a1a0a5eccc32e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7bee4a1e548e177</t>
+          <t>https://www.indeed.com/viewjob?jk=8993a2c0de0e70e1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
+          <t>RPA Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a54ac0922147b15</t>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Solutions Designer</t>
+          <t>Senior Software Engineer – Product</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Re:Build Manufacturing</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Event Hubs, Scala, Kafka, Snowflake, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42d7826852e5a12b</t>
+          <t>https://www.indeed.com/viewjob?jk=61d08f5c56b39289</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Network/Systems Engineer/DBA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CCSI</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, MySQL, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, DataOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82f25ac0bbe1b8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=0ebbf24573d559b5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Development Operations Engineer</t>
+          <t>Senior Solutions Designer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git, Azure Monitor, Python</t>
+          <t>AWS, RDS, Databricks, Event Hubs, Scala, Kafka, Snowflake, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730302ab09184768</t>
+          <t>https://www.indeed.com/viewjob?jk=42d7826852e5a12b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7fd121bc0e2325</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb8dc7b4cca4c33</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f41d2b8270473c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=a7bee4a1e548e177</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a6494cda8c81441</t>
+          <t>https://www.indeed.com/viewjob?jk=5a54ac0922147b15</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Network/Systems Engineer/DBA</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>CCSI</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, MySQL, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7dbdf6ce237b13d</t>
+          <t>https://www.indeed.com/viewjob?jk=82f25ac0bbe1b8ca</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Appian Dev-Reporting &amp; Analytics</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Verisure</t>
+          <t>Department of Finance</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Uniontown, OH, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, REST API integration, Power BI, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, ETL, Power BI, Tableau, AKS</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c374eb71cdd5829a</t>
+          <t>https://www.indeed.com/viewjob?jk=88aacc0c7f29344d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>[REMOTE] Senior Platform Software Engineer- Oracle Clinical Digital Assistant</t>
+          <t>Solutions Engineer - Data Visualization</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f3fde4ed90357e</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfe4bd64f8f496f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
+          <t>Senior Development Operations Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Asurion</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, AWS CodePipeline, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a35189b0c83845</t>
+          <t>https://www.indeed.com/viewjob?jk=730302ab09184768</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Visualization</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfe4bd64f8f496f</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7fd121bc0e2325</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Appian Dev-Reporting &amp; Analytics</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Department of Finance</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, ETL, Power BI, Tableau, AKS</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,182 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88aacc0c7f29344d</t>
+          <t>https://www.indeed.com/viewjob?jk=f41d2b8270473c0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a6494cda8c81441</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Aivra Health</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7dbdf6ce237b13d</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Verisure</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Uniontown, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, SQL Server, REST API integration, Power BI, CI/CD, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c374eb71cdd5829a</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>[REMOTE] Senior Platform Software Engineer- Oracle Clinical Digital Assistant</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23f3fde4ed90357e</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Asurion</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, AWS CodePipeline, Docker</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4a35189b0c83845</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-15.xlsx
+++ b/results/job_matches_2026-07-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Developer - IT</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>GE Appliances</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Arlington Heights, IL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Azure, GCP, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23c6690878cc61dc</t>
+          <t>https://www.indeed.com/viewjob?jk=f488fb42bdd9a3e5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Solutions Architect - Airflow (West Coast)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GE Appliances</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f488fb42bdd9a3e5</t>
+          <t>https://www.indeed.com/viewjob?jk=563d41613641e2d6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (West Coast)</t>
+          <t>AWS Full Stack Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563d41613641e2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e643625eb77abd14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AWS Full Stack Engineer</t>
+          <t>DataHub Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, IAM, RDS, Scala</t>
+          <t>AWS, S3, IAM, RDS, Azure, Kafka, Kafka Connect, Oracle, MySQL, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e643625eb77abd14</t>
+          <t>https://www.indeed.com/viewjob?jk=5423277344900438</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DataHub Developer</t>
+          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Kafka, Kafka Connect, Oracle, MySQL, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5423277344900438</t>
+          <t>https://www.indeed.com/viewjob?jk=4f9fcd187c753bef</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f9fcd187c753bef</t>
+          <t>https://www.indeed.com/viewjob?jk=751a33e38e145115</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
+          <t>Artificial Intelligence Senior Data Scientist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=751a33e38e145115</t>
+          <t>https://www.indeed.com/viewjob?jk=4a48e7242a74c765</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Cloud Ops Engineer I - SRE</t>
+          <t>Data Engineer- BI Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CaseWorthy</t>
+          <t>Diversified Gas &amp; Oil</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d69f297c014e4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d9cd4d53bb42fc00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Senior Cloud Ops Engineer I - SRE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Escalent</t>
+          <t>CaseWorthy</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45d62ba2dc0bd875</t>
+          <t>https://www.indeed.com/viewjob?jk=9d69f297c014e4a1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>Escalent</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7481c6f102626c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=45d62ba2dc0bd875</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer - Front-End Focused</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>STAND TOGETHER</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, MongoDB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3221281fdf023197</t>
+          <t>https://www.indeed.com/viewjob?jk=7481c6f102626c6e</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data &amp; Analytics Platform (Snowflake/dbt)</t>
+          <t>Spark Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, Power BI, Tableau, DataOps</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f401900b912197cd</t>
+          <t>https://www.indeed.com/viewjob?jk=2cb65007f4e4e07a</t>
         </is>
       </c>
     </row>
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cb65007f4e4e07a</t>
+          <t>https://www.indeed.com/viewjob?jk=e7beab78b75a48b8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Spark Engineer</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7beab78b75a48b8</t>
+          <t>https://www.indeed.com/viewjob?jk=f722c5b892610593</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Engineer</t>
+          <t>Sr Engineer, Data &amp; Analytics Platform (Snowflake/dbt)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c44bbcac30a87c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f401900b912197cd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Engineer</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,19 +2106,19 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc37b1c10548573</t>
+          <t>https://www.indeed.com/viewjob?jk=decf563d2df9d00c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sigma Report Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Tachyon Technologies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Scala, ETL, Tableau, Terraform, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221a044944e1b41d</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8d0798b16bd29a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Forward Deployed Engineer - AI SOC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decf563d2df9d00c</t>
+          <t>https://www.indeed.com/viewjob?jk=29fa83f558965646</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sigma Report Developer</t>
+          <t>Senior AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tachyon Technologies</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8d0798b16bd29a</t>
+          <t>https://www.indeed.com/viewjob?jk=0c44bbcac30a87c2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - AI SOC</t>
+          <t>Senior AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fa83f558965646</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc37b1c10548573</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Quality and Data Engineer</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Vance, AL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a36a0ff08797a70</t>
+          <t>https://www.indeed.com/viewjob?jk=be21268d9d981efd</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be21268d9d981efd</t>
+          <t>https://www.indeed.com/viewjob?jk=f756de42016efc57</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f756de42016efc57</t>
+          <t>https://www.indeed.com/viewjob?jk=abc756e24b7ebb78</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
+          <t>Senior Snowflake Data Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, S3, RDS, Scala, Snowflake, DynamoDB, ELT, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abc756e24b7ebb78</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a8050d86dd2bf8</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Platform Engineer (Hybrid)</t>
+          <t>Quality and Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>Mercedes-Benz Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Vance, AL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, Snowflake, DynamoDB, ELT, Splunk, MLflow</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a8050d86dd2bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=3a36a0ff08797a70</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer- Hybrid</t>
+          <t>Senior .NET and SSRS Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Match Made Tech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, Scala, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936d9e38993af00c</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c8883b0dd19abf</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior .NET and SSRS Developer</t>
+          <t>Full Stack Developer III - Private Markets Applications</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c8883b0dd19abf</t>
+          <t>https://www.indeed.com/viewjob?jk=04f2e93224c9a790</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full Stack Developer III - Private Markets Applications</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f2e93224c9a790</t>
+          <t>https://www.indeed.com/viewjob?jk=bf57c7d8b4b2d9e4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf57c7d8b4b2d9e4</t>
+          <t>https://www.indeed.com/viewjob?jk=032b8db4bfd5e6d8</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032b8db4bfd5e6d8</t>
+          <t>https://www.indeed.com/viewjob?jk=46f856d080d24d05</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f856d080d24d05</t>
+          <t>https://www.indeed.com/viewjob?jk=19153bb3202f8519</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19153bb3202f8519</t>
+          <t>https://www.indeed.com/viewjob?jk=ee7a2d23cf0b0fbe</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee7a2d23cf0b0fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=00a3e62df8c707d8</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3e62df8c707d8</t>
+          <t>https://www.indeed.com/viewjob?jk=779a1a0a5eccc32e</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=779a1a0a5eccc32e</t>
+          <t>https://www.indeed.com/viewjob?jk=8993a2c0de0e70e1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>RPA Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8993a2c0de0e70e1</t>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>RPA Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Datadrive</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Tableau, DataOps, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f20a50010d3a4e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Product</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Re:Build Manufacturing</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, DataOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d08f5c56b39289</t>
+          <t>https://www.indeed.com/viewjob?jk=0ebbf24573d559b5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer – Product</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Re:Build Manufacturing</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, DataOps</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ebbf24573d559b5</t>
+          <t>https://www.indeed.com/viewjob?jk=61d08f5c56b39289</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Solutions Designer</t>
+          <t>Performance Engineer, Information technology</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>ServiceLink</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Event Hubs, Scala, Kafka, Snowflake, ETL, Power BI, Tableau</t>
+          <t>API Gateway, RDS, Azure, Event Hubs, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, AKS</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42d7826852e5a12b</t>
+          <t>https://www.indeed.com/viewjob?jk=f3af50fd888d2a26</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
+          <t>Specialist, Software Engineer - Test Automation Developer (Ruby &amp; Playwright)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb8dc7b4cca4c33</t>
+          <t>https://www.indeed.com/viewjob?jk=f00ee1189eddb9b1</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7bee4a1e548e177</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb8dc7b4cca4c33</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a54ac0922147b15</t>
+          <t>https://www.indeed.com/viewjob?jk=a7bee4a1e548e177</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Network/Systems Engineer/DBA</t>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CCSI</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, MySQL, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82f25ac0bbe1b8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=5a54ac0922147b15</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Appian Dev-Reporting &amp; Analytics</t>
+          <t>Network/Systems Engineer/DBA</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Department of Finance</t>
+          <t>CCSI</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, ETL, Power BI, Tableau, AKS</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, MySQL, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88aacc0c7f29344d</t>
+          <t>https://www.indeed.com/viewjob?jk=82f25ac0bbe1b8ca</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Visualization</t>
+          <t>Appian Dev-Reporting &amp; Analytics</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Department of Finance</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, ETL, Power BI, Tableau, AKS</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfe4bd64f8f496f</t>
+          <t>https://www.indeed.com/viewjob?jk=88aacc0c7f29344d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Development Operations Engineer</t>
+          <t>Solutions Engineer - Data Visualization</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git, Azure Monitor, Python</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730302ab09184768</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfe4bd64f8f496f</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Development Operations Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7fd121bc0e2325</t>
+          <t>https://www.indeed.com/viewjob?jk=730302ab09184768</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f41d2b8270473c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7fd121bc0e2325</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a6494cda8c81441</t>
+          <t>https://www.indeed.com/viewjob?jk=f41d2b8270473c0a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7dbdf6ce237b13d</t>
+          <t>https://www.indeed.com/viewjob?jk=8a6494cda8c81441</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Verisure</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Uniontown, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, REST API integration, Power BI, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c374eb71cdd5829a</t>
+          <t>https://www.indeed.com/viewjob?jk=e7dbdf6ce237b13d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>[REMOTE] Senior Platform Software Engineer- Oracle Clinical Digital Assistant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Verisure</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Uniontown, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, SQL Server, REST API integration, Power BI, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f3fde4ed90357e</t>
+          <t>https://www.indeed.com/viewjob?jk=c374eb71cdd5829a</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
+          <t>[REMOTE] Senior Platform Software Engineer- Oracle Clinical Digital Assistant</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Asurion</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,15 +3706,50 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23f3fde4ed90357e</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Asurion</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
           <t>AWS, ECS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, AWS CodePipeline, Docker</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b4a35189b0c83845</t>
         </is>

--- a/results/job_matches_2026-07-15.xlsx
+++ b/results/job_matches_2026-07-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GE Appliances</t>
+          <t>Berkley</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, dbt, MLflow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f488fb42bdd9a3e5</t>
+          <t>https://www.indeed.com/viewjob?jk=7656191539f10c8f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (West Coast)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>GE Appliances</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563d41613641e2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=f488fb42bdd9a3e5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AWS Full Stack Engineer</t>
+          <t>Senior Solutions Architect - Airflow (West Coast)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, IAM, RDS, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e643625eb77abd14</t>
+          <t>https://www.indeed.com/viewjob?jk=563d41613641e2d6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DataHub Developer</t>
+          <t>AWS Full Stack Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Kafka, Kafka Connect, Oracle, MySQL, ETL</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5423277344900438</t>
+          <t>https://www.indeed.com/viewjob?jk=e643625eb77abd14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
+          <t>DataHub Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Kafka, Kafka Connect, Oracle, MySQL, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f9fcd187c753bef</t>
+          <t>https://www.indeed.com/viewjob?jk=5423277344900438</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=751a33e38e145115</t>
+          <t>https://www.indeed.com/viewjob?jk=4f9fcd187c753bef</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Senior Data Scientist</t>
+          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a48e7242a74c765</t>
+          <t>https://www.indeed.com/viewjob?jk=751a33e38e145115</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Artificial Intelligence Senior Data Scientist</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ideas2IT Technology Services</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tennyson, IN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,69 +1606,69 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c514f50b938a8dc</t>
+          <t>https://www.indeed.com/viewjob?jk=4a48e7242a74c765</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer- BI Developer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Diversified Gas &amp; Oil</t>
+          <t>Ideas2IT Technology Services</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Tennyson, IN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9cd4d53bb42fc00</t>
+          <t>https://www.indeed.com/viewjob?jk=3c514f50b938a8dc</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Cloud Ops Engineer I - SRE</t>
+          <t>Data Engineer- BI Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CaseWorthy</t>
+          <t>Diversified Gas &amp; Oil</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d69f297c014e4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d9cd4d53bb42fc00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Senior Cloud Ops Engineer I - SRE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Escalent</t>
+          <t>CaseWorthy</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45d62ba2dc0bd875</t>
+          <t>https://www.indeed.com/viewjob?jk=9d69f297c014e4a1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>Escalent</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7481c6f102626c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=45d62ba2dc0bd875</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69cd7125f7a833</t>
+          <t>https://www.indeed.com/viewjob?jk=7481c6f102626c6e</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c09787e1cb8cb395</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69cd7125f7a833</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4ad7ea1b58a31e</t>
+          <t>https://www.indeed.com/viewjob?jk=c09787e1cb8cb395</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc726639aa959a6</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4ad7ea1b58a31e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Development Engineer I - ArcGIS Enterprise</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b08010c09c91435</t>
+          <t>https://www.indeed.com/viewjob?jk=1cc726639aa959a6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Spark Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NextAmp LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>ECS, RDS, Snowflake, Oracle, SQL Server, Dimensional Modeling, Kimball, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cb65007f4e4e07a</t>
+          <t>https://www.indeed.com/viewjob?jk=112573c8edf11915</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Spark Engineer</t>
+          <t>Software Development Engineer I - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7beab78b75a48b8</t>
+          <t>https://www.indeed.com/viewjob?jk=0b08010c09c91435</t>
         </is>
       </c>
     </row>
@@ -2113,12 +2113,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sigma Report Developer</t>
+          <t>Forward Deployed Engineer - AI SOC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tachyon Technologies</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8d0798b16bd29a</t>
+          <t>https://www.indeed.com/viewjob?jk=29fa83f558965646</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - AI SOC</t>
+          <t>Senior AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fa83f558965646</t>
+          <t>https://www.indeed.com/viewjob?jk=0c44bbcac30a87c2</t>
         </is>
       </c>
     </row>
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c44bbcac30a87c2</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc37b1c10548573</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Engineer</t>
+          <t>Senior .NET Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Blob Storage, YARN, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc37b1c10548573</t>
+          <t>https://www.indeed.com/viewjob?jk=52c472962c791de2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>Advanced Software Engineer- Full Stack Cloud Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, YARN, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52c472962c791de2</t>
+          <t>https://www.indeed.com/viewjob?jk=78950b770ed7417f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Advanced Software Engineer- Full Stack Cloud Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>El Toro.com</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78950b770ed7417f</t>
+          <t>https://www.indeed.com/viewjob?jk=d42d84e2b583adb0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>El Toro.com</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42d84e2b583adb0</t>
+          <t>https://www.indeed.com/viewjob?jk=be21268d9d981efd</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be21268d9d981efd</t>
+          <t>https://www.indeed.com/viewjob?jk=f756de42016efc57</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f756de42016efc57</t>
+          <t>https://www.indeed.com/viewjob?jk=abc756e24b7ebb78</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
+          <t>Senior Snowflake Data Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, S3, RDS, Scala, Snowflake, DynamoDB, ELT, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abc756e24b7ebb78</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a8050d86dd2bf8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Platform Engineer (Hybrid)</t>
+          <t>Quality and Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>Mercedes-Benz Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Vance, AL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, Snowflake, DynamoDB, ELT, Splunk, MLflow</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a8050d86dd2bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=3a36a0ff08797a70</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Quality and Data Engineer</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Vance, AL, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a36a0ff08797a70</t>
+          <t>https://www.indeed.com/viewjob?jk=b36c700922532ac2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Azure Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36c700922532ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=32d19f755ee8489a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, PySpark, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d19f755ee8489a</t>
+          <t>https://www.indeed.com/viewjob?jk=4223c8030b51f20b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>2026-2027 Information Technology - Software Engineer - Intern</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, PySpark, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4223c8030b51f20b</t>
+          <t>https://www.indeed.com/viewjob?jk=eab14599c79da82b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-2027 Information Technology - Software Engineer - Intern</t>
+          <t>2026-2027 Information Technology - Software Engineer - Full-Time</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab14599c79da82b</t>
+          <t>https://www.indeed.com/viewjob?jk=d6578ea1eb5e5142</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-2027 Information Technology - Software Engineer - Full-Time</t>
+          <t>Senior .NET and SSRS Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6578ea1eb5e5142</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c8883b0dd19abf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior .NET and SSRS Developer</t>
+          <t>Full Stack Developer III - Private Markets Applications</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c8883b0dd19abf</t>
+          <t>https://www.indeed.com/viewjob?jk=04f2e93224c9a790</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack Developer III - Private Markets Applications</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f2e93224c9a790</t>
+          <t>https://www.indeed.com/viewjob?jk=bf57c7d8b4b2d9e4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf57c7d8b4b2d9e4</t>
+          <t>https://www.indeed.com/viewjob?jk=032b8db4bfd5e6d8</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032b8db4bfd5e6d8</t>
+          <t>https://www.indeed.com/viewjob?jk=46f856d080d24d05</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f856d080d24d05</t>
+          <t>https://www.indeed.com/viewjob?jk=19153bb3202f8519</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19153bb3202f8519</t>
+          <t>https://www.indeed.com/viewjob?jk=ee7a2d23cf0b0fbe</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee7a2d23cf0b0fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=00a3e62df8c707d8</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3e62df8c707d8</t>
+          <t>https://www.indeed.com/viewjob?jk=779a1a0a5eccc32e</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=779a1a0a5eccc32e</t>
+          <t>https://www.indeed.com/viewjob?jk=8993a2c0de0e70e1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>RPA Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8993a2c0de0e70e1</t>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>RPA Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Datadrive</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Tableau, DataOps, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f20a50010d3a4e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Datadrive</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Tableau, DataOps, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, DataOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f20a50010d3a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=0ebbf24573d559b5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer – Product</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Re:Build Manufacturing</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, DataOps</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ebbf24573d559b5</t>
+          <t>https://www.indeed.com/viewjob?jk=61d08f5c56b39289</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Product</t>
+          <t>Specialist, Software Engineer - Test Automation Developer (Ruby &amp; Playwright)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Re:Build Manufacturing</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d08f5c56b39289</t>
+          <t>https://www.indeed.com/viewjob?jk=f00ee1189eddb9b1</t>
         </is>
       </c>
     </row>
@@ -3233,17 +3233,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Specialist, Software Engineer - Test Automation Developer (Ruby &amp; Playwright)</t>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins, Git</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f00ee1189eddb9b1</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb8dc7b4cca4c33</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb8dc7b4cca4c33</t>
+          <t>https://www.indeed.com/viewjob?jk=a7bee4a1e548e177</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7bee4a1e548e177</t>
+          <t>https://www.indeed.com/viewjob?jk=5a54ac0922147b15</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
+          <t>Network/Systems Engineer/DBA</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>CCSI</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, MySQL, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a54ac0922147b15</t>
+          <t>https://www.indeed.com/viewjob?jk=82f25ac0bbe1b8ca</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Network/Systems Engineer/DBA</t>
+          <t>Solutions Engineer - Data Visualization</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CCSI</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, MySQL, Splunk, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82f25ac0bbe1b8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfe4bd64f8f496f</t>
         </is>
       </c>
     </row>
@@ -3443,17 +3443,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Visualization</t>
+          <t>Senior Development Operations Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfe4bd64f8f496f</t>
+          <t>https://www.indeed.com/viewjob?jk=730302ab09184768</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Development Operations Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git, Azure Monitor, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730302ab09184768</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7fd121bc0e2325</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7fd121bc0e2325</t>
+          <t>https://www.indeed.com/viewjob?jk=f41d2b8270473c0a</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f41d2b8270473c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=8a6494cda8c81441</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a6494cda8c81441</t>
+          <t>https://www.indeed.com/viewjob?jk=e7dbdf6ce237b13d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>Verisure</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Uniontown, OH, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>AWS, Azure, Scala, SQL Server, REST API integration, Power BI, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7dbdf6ce237b13d</t>
+          <t>https://www.indeed.com/viewjob?jk=c374eb71cdd5829a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>[REMOTE] Senior Platform Software Engineer- Oracle Clinical Digital Assistant</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Verisure</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Uniontown, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, REST API integration, Power BI, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c374eb71cdd5829a</t>
+          <t>https://www.indeed.com/viewjob?jk=23f3fde4ed90357e</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>[REMOTE] Senior Platform Software Engineer- Oracle Clinical Digital Assistant</t>
+          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Asurion</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,50 +3706,15 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, AWS CodePipeline, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23f3fde4ed90357e</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Asurion</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, AWS CodePipeline, Docker</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b4a35189b0c83845</t>
         </is>

--- a/results/job_matches_2026-07-15.xlsx
+++ b/results/job_matches_2026-07-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Azure, Databricks, Google Cloud Platform, GCP, Hive, HBase, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78eadef287e1b0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=e085be8f0f2f681d</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e085be8f0f2f681d</t>
+          <t>https://www.indeed.com/viewjob?jk=b192e5946ee2ce27</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b192e5946ee2ce27</t>
+          <t>https://www.indeed.com/viewjob?jk=93c17e2e00004cf8</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c17e2e00004cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d9682d5f343e62</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Data Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d9682d5f343e62</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c9310d05771935</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure Data Architect</t>
+          <t>Junior Architect / Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c9310d05771935</t>
+          <t>https://www.indeed.com/viewjob?jk=7e53a2ba6f9a4021</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Junior Architect / Senior Data Engineer - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, RDS, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e53a2ba6f9a4021</t>
+          <t>https://www.indeed.com/viewjob?jk=588555361d1bf2c2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer Remote - US • Remote</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Daxko</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, RDS, Google Cloud Platform, GCP</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Athena, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=588555361d1bf2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d212feaf575e2588</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Remote - US • Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d212feaf575e2588</t>
+          <t>https://www.indeed.com/viewjob?jk=419f9c53a083aba9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data AI Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Daxko</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Athena, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=419f9c53a083aba9</t>
+          <t>https://www.indeed.com/viewjob?jk=9de5ac8d42dd8ec2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data AI Architect</t>
+          <t>Azure Data Architect (remote US)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>News Corp</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9de5ac8d42dd8ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=d584a94be46cf8b0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Azure Data Architect (remote US)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>News Corp</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d584a94be46cf8b0</t>
+          <t>https://www.indeed.com/viewjob?jk=3720530c1ac33814</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Glue/Python/Pyspark</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3720530c1ac33814</t>
+          <t>https://www.indeed.com/viewjob?jk=0bd064010356a824</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III - Glue/Python/Pyspark</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bd064010356a824</t>
+          <t>https://www.indeed.com/viewjob?jk=b9be95a71934961d</t>
         </is>
       </c>
     </row>
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9be95a71934961d</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf05ce3284e6a20</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Itero Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>AWS, Glue, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf05ce3284e6a20</t>
+          <t>https://www.indeed.com/viewjob?jk=e304be37d5897728</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e304be37d5897728</t>
+          <t>https://www.indeed.com/viewjob?jk=9724f20b3e8cf9d3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Senior Data Management Professional - Data Engineering - Entities</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Itero Group</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9724f20b3e8cf9d3</t>
+          <t>https://www.indeed.com/viewjob?jk=00a24491194c9938</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Management Professional - Data Engineering - Entities</t>
+          <t>Senior Data Scientist - Artificial Intelligence</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,69 +1151,69 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a24491194c9938</t>
+          <t>https://www.indeed.com/viewjob?jk=7cf8977f54a3cd6f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Artificial Intelligence</t>
+          <t>Senior Cloud Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cf8977f54a3cd6f</t>
+          <t>https://www.indeed.com/viewjob?jk=0426c9944a6312e8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0426c9944a6312e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f5d11d7b626cfc</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f5d11d7b626cfc</t>
+          <t>https://www.indeed.com/viewjob?jk=a407a20c56f80680</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Berkley</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, dbt, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7656191539f10c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=9690379ea46f2be7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GE Appliances</t>
+          <t>Berkley</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, dbt, MLflow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f488fb42bdd9a3e5</t>
+          <t>https://www.indeed.com/viewjob?jk=7656191539f10c8f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (West Coast)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>GE Appliances</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563d41613641e2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=f488fb42bdd9a3e5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AWS Full Stack Engineer</t>
+          <t>Senior Solutions Architect - Airflow (West Coast)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, IAM, RDS, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e643625eb77abd14</t>
+          <t>https://www.indeed.com/viewjob?jk=563d41613641e2d6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DataHub Developer</t>
+          <t>AWS Full Stack Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Kafka, Kafka Connect, Oracle, MySQL, ETL</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5423277344900438</t>
+          <t>https://www.indeed.com/viewjob?jk=e643625eb77abd14</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
+          <t>DataHub Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Kafka, Kafka Connect, Oracle, MySQL, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f9fcd187c753bef</t>
+          <t>https://www.indeed.com/viewjob?jk=5423277344900438</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=751a33e38e145115</t>
+          <t>https://www.indeed.com/viewjob?jk=4f9fcd187c753bef</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Senior Data Scientist</t>
+          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a48e7242a74c765</t>
+          <t>https://www.indeed.com/viewjob?jk=751a33e38e145115</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Artificial Intelligence Senior Data Scientist</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ideas2IT Technology Services</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tennyson, IN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,69 +1641,69 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c514f50b938a8dc</t>
+          <t>https://www.indeed.com/viewjob?jk=4a48e7242a74c765</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer- BI Developer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Diversified Gas &amp; Oil</t>
+          <t>Ideas2IT Technology Services</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Tennyson, IN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9cd4d53bb42fc00</t>
+          <t>https://www.indeed.com/viewjob?jk=3c514f50b938a8dc</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Cloud Ops Engineer I - SRE</t>
+          <t>Data Engineer- BI Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CaseWorthy</t>
+          <t>Diversified Gas &amp; Oil</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d69f297c014e4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d9cd4d53bb42fc00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Senior Cloud Ops Engineer I - SRE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Escalent</t>
+          <t>CaseWorthy</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45d62ba2dc0bd875</t>
+          <t>https://www.indeed.com/viewjob?jk=9d69f297c014e4a1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>Escalent</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7481c6f102626c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=45d62ba2dc0bd875</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69cd7125f7a833</t>
+          <t>https://www.indeed.com/viewjob?jk=7481c6f102626c6e</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c09787e1cb8cb395</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69cd7125f7a833</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4ad7ea1b58a31e</t>
+          <t>https://www.indeed.com/viewjob?jk=c09787e1cb8cb395</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc726639aa959a6</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4ad7ea1b58a31e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NextAmp LLC</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ECS, RDS, Snowflake, Oracle, SQL Server, Dimensional Modeling, Kimball, Star Schema, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=112573c8edf11915</t>
+          <t>https://www.indeed.com/viewjob?jk=1cc726639aa959a6</t>
         </is>
       </c>
     </row>
@@ -2008,35 +2008,35 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>NextAmp LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>ECS, RDS, Snowflake, Oracle, SQL Server, Dimensional Modeling, Kimball, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f722c5b892610593</t>
+          <t>https://www.indeed.com/viewjob?jk=112573c8edf11915</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decf563d2df9d00c</t>
+          <t>https://www.indeed.com/viewjob?jk=f722c5b892610593</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - AI SOC</t>
+          <t>Developer-Full Stack Senior</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fa83f558965646</t>
+          <t>https://www.indeed.com/viewjob?jk=45e9f859d9d42bd7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Engineer</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c44bbcac30a87c2</t>
+          <t>https://www.indeed.com/viewjob?jk=decf563d2df9d00c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Engineer</t>
+          <t>Forward Deployed Engineer - AI SOC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc37b1c10548573</t>
+          <t>https://www.indeed.com/viewjob?jk=29fa83f558965646</t>
         </is>
       </c>
     </row>
@@ -2323,25 +2323,25 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Senior AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be21268d9d981efd</t>
+          <t>https://www.indeed.com/viewjob?jk=0c44bbcac30a87c2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Senior AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f756de42016efc57</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc37b1c10548573</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
+          <t>Quality and Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>Mercedes-Benz Group</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Vance, AL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abc756e24b7ebb78</t>
+          <t>https://www.indeed.com/viewjob?jk=3a36a0ff08797a70</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Platform Engineer (Hybrid)</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, Snowflake, DynamoDB, ELT, Splunk, MLflow</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a8050d86dd2bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=be21268d9d981efd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Quality and Data Engineer</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Vance, AL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a36a0ff08797a70</t>
+          <t>https://www.indeed.com/viewjob?jk=f756de42016efc57</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36c700922532ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=abc756e24b7ebb78</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>Senior Snowflake Data Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, Scala, Snowflake, DynamoDB, ELT, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d19f755ee8489a</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a8050d86dd2bf8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, PySpark, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4223c8030b51f20b</t>
+          <t>https://www.indeed.com/viewjob?jk=b36c700922532ac2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-2027 Information Technology - Software Engineer - Intern</t>
+          <t>Azure Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab14599c79da82b</t>
+          <t>https://www.indeed.com/viewjob?jk=32d19f755ee8489a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-2027 Information Technology - Software Engineer - Full-Time</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, PySpark, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6578ea1eb5e5142</t>
+          <t>https://www.indeed.com/viewjob?jk=4223c8030b51f20b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior .NET and SSRS Developer</t>
+          <t>2026-2027 Information Technology - Software Engineer - Intern</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c8883b0dd19abf</t>
+          <t>https://www.indeed.com/viewjob?jk=eab14599c79da82b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Developer III - Private Markets Applications</t>
+          <t>2026-2027 Information Technology - Software Engineer - Full-Time</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, ETL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f2e93224c9a790</t>
+          <t>https://www.indeed.com/viewjob?jk=d6578ea1eb5e5142</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior .NET and SSRS Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf57c7d8b4b2d9e4</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c8883b0dd19abf</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Full Stack Developer III - Private Markets Applications</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032b8db4bfd5e6d8</t>
+          <t>https://www.indeed.com/viewjob?jk=04f2e93224c9a790</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f856d080d24d05</t>
+          <t>https://www.indeed.com/viewjob?jk=bf57c7d8b4b2d9e4</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19153bb3202f8519</t>
+          <t>https://www.indeed.com/viewjob?jk=032b8db4bfd5e6d8</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee7a2d23cf0b0fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=46f856d080d24d05</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3e62df8c707d8</t>
+          <t>https://www.indeed.com/viewjob?jk=19153bb3202f8519</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=779a1a0a5eccc32e</t>
+          <t>https://www.indeed.com/viewjob?jk=ee7a2d23cf0b0fbe</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8993a2c0de0e70e1</t>
+          <t>https://www.indeed.com/viewjob?jk=00a3e62df8c707d8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>RPA Engineer</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+          <t>https://www.indeed.com/viewjob?jk=779a1a0a5eccc32e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Datadrive</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Tableau, DataOps, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f20a50010d3a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=8993a2c0de0e70e1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>RPA Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, DataOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ebbf24573d559b5</t>
+          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
         </is>
       </c>
     </row>
@@ -3163,17 +3163,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Specialist, Software Engineer - Test Automation Developer (Ruby &amp; Playwright)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Datadrive</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Tableau, DataOps, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f00ee1189eddb9b1</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f20a50010d3a4e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Performance Engineer, Information technology</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ServiceLink</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Event Hubs, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, DataOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3af50fd888d2a26</t>
+          <t>https://www.indeed.com/viewjob?jk=0ebbf24573d559b5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
+          <t>Performance Engineer, Information technology</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>ServiceLink</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>API Gateway, RDS, Azure, Event Hubs, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, AKS</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb8dc7b4cca4c33</t>
+          <t>https://www.indeed.com/viewjob?jk=f3af50fd888d2a26</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
+          <t>Specialist, Software Engineer - Test Automation Developer (Ruby &amp; Playwright)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,17 +3286,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7bee4a1e548e177</t>
+          <t>https://www.indeed.com/viewjob?jk=f00ee1189eddb9b1</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a54ac0922147b15</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb8dc7b4cca4c33</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Network/Systems Engineer/DBA</t>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CCSI</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, MySQL, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82f25ac0bbe1b8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=a7bee4a1e548e177</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Visualization</t>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfe4bd64f8f496f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a54ac0922147b15</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Appian Dev-Reporting &amp; Analytics</t>
+          <t>Network/Systems Engineer/DBA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Department of Finance</t>
+          <t>CCSI</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, ETL, Power BI, Tableau, AKS</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, MySQL, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88aacc0c7f29344d</t>
+          <t>https://www.indeed.com/viewjob?jk=82f25ac0bbe1b8ca</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Development Operations Engineer</t>
+          <t>Solutions Engineer - Data Visualization</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git, Azure Monitor, Python</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730302ab09184768</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfe4bd64f8f496f</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Appian Dev-Reporting &amp; Analytics</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Department of Finance</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, ETL, Power BI, Tableau, AKS</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7fd121bc0e2325</t>
+          <t>https://www.indeed.com/viewjob?jk=88aacc0c7f29344d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Development Operations Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f41d2b8270473c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=730302ab09184768</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a6494cda8c81441</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7fd121bc0e2325</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7dbdf6ce237b13d</t>
+          <t>https://www.indeed.com/viewjob?jk=f41d2b8270473c0a</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Verisure</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Uniontown, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, REST API integration, Power BI, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,19 +3646,19 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c374eb71cdd5829a</t>
+          <t>https://www.indeed.com/viewjob?jk=8a6494cda8c81441</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>[REMOTE] Senior Platform Software Engineer- Oracle Clinical Digital Assistant</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f3fde4ed90357e</t>
+          <t>https://www.indeed.com/viewjob?jk=e7dbdf6ce237b13d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Asurion</t>
+          <t>Verisure</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Uniontown, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,15 +3706,50 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
+          <t>AWS, Azure, Scala, SQL Server, REST API integration, Power BI, CI/CD, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c374eb71cdd5829a</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Asurion</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
           <t>AWS, ECS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, AWS CodePipeline, Docker</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b4a35189b0c83845</t>
         </is>

--- a/results/job_matches_2026-07-15.xlsx
+++ b/results/job_matches_2026-07-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,7 +513,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e085be8f0f2f681d</t>
+          <t>https://www.indeed.com/viewjob?jk=b192e5946ee2ce27</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b192e5946ee2ce27</t>
+          <t>https://www.indeed.com/viewjob?jk=93c17e2e00004cf8</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c17e2e00004cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d9682d5f343e62</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d9682d5f343e62</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c9310d05771935</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Azure Data Architect</t>
+          <t>Junior Architect / Senior Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c9310d05771935</t>
+          <t>https://www.indeed.com/viewjob?jk=7e53a2ba6f9a4021</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Junior Architect / Senior Data Engineer - Remote</t>
+          <t>Senior Data Engineer Remote - US • Remote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Daxko</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Athena, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e53a2ba6f9a4021</t>
+          <t>https://www.indeed.com/viewjob?jk=d212feaf575e2588</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Daxko</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, IAM, RDS, Google Cloud Platform, GCP</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Athena, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=588555361d1bf2c2</t>
+          <t>https://www.indeed.com/viewjob?jk=419f9c53a083aba9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Remote - US • Remote</t>
+          <t>Data AI Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Daxko</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Athena, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d212feaf575e2588</t>
+          <t>https://www.indeed.com/viewjob?jk=9de5ac8d42dd8ec2</t>
         </is>
       </c>
     </row>
@@ -788,20 +788,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Daxko</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Athena, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=419f9c53a083aba9</t>
+          <t>https://www.indeed.com/viewjob?jk=3720530c1ac33814</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data AI Architect</t>
+          <t>Software Engineer III - Glue/Python/Pyspark</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9de5ac8d42dd8ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=0bd064010356a824</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Azure Data Architect (remote US)</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>News Corp</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d584a94be46cf8b0</t>
+          <t>https://www.indeed.com/viewjob?jk=b9be95a71934961d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Modivcare</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3720530c1ac33814</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf05ce3284e6a20</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer III - Glue/Python/Pyspark</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Itero Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bd064010356a824</t>
+          <t>https://www.indeed.com/viewjob?jk=e304be37d5897728</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Senior Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Itero Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>AWS, Glue, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9be95a71934961d</t>
+          <t>https://www.indeed.com/viewjob?jk=9724f20b3e8cf9d3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Senior Data Management Professional - Data Engineering - Entities</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf05ce3284e6a20</t>
+          <t>https://www.indeed.com/viewjob?jk=00a24491194c9938</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Senior Data Scientist - Artificial Intelligence</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Itero Group</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e304be37d5897728</t>
+          <t>https://www.indeed.com/viewjob?jk=7cf8977f54a3cd6f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Senior Cloud Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Itero Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9724f20b3e8cf9d3</t>
+          <t>https://www.indeed.com/viewjob?jk=0426c9944a6312e8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Management Professional - Data Engineering - Entities</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a24491194c9938</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f5d11d7b626cfc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Artificial Intelligence</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cf8977f54a3cd6f</t>
+          <t>https://www.indeed.com/viewjob?jk=a407a20c56f80680</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Remote</t>
+          <t>AI Native Developer- Europe</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0426c9944a6312e8</t>
+          <t>https://www.indeed.com/viewjob?jk=444a0e6bd539f82b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Native Builder-Europe</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,102 +1231,102 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f5d11d7b626cfc</t>
+          <t>https://www.indeed.com/viewjob?jk=ae934e8451ebc14c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Moffitt Cancer Center</t>
+          <t>Berkley</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, dbt, MLflow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a407a20c56f80680</t>
+          <t>https://www.indeed.com/viewjob?jk=7656191539f10c8f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Native Developer- Europe</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=444a0e6bd539f82b</t>
+          <t>https://www.indeed.com/viewjob?jk=9690379ea46f2be7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Native Builder-Europe</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>GE Appliances</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae934e8451ebc14c</t>
+          <t>https://www.indeed.com/viewjob?jk=f488fb42bdd9a3e5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Solutions Architect - Airflow (West Coast)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9690379ea46f2be7</t>
+          <t>https://www.indeed.com/viewjob?jk=563d41613641e2d6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>AWS Full Stack Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Berkley</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, dbt, MLflow</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7656191539f10c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=e643625eb77abd14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>DataHub Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GE Appliances</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, S3, IAM, RDS, Azure, Kafka, Kafka Connect, Oracle, MySQL, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f488fb42bdd9a3e5</t>
+          <t>https://www.indeed.com/viewjob?jk=5423277344900438</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (West Coast)</t>
+          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563d41613641e2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=4f9fcd187c753bef</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AWS Full Stack Engineer</t>
+          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,29 +1501,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e643625eb77abd14</t>
+          <t>https://www.indeed.com/viewjob?jk=751a33e38e145115</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DataHub Developer</t>
+          <t>Artificial Intelligence Senior Data Scientist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Kafka, Kafka Connect, Oracle, MySQL, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5423277344900438</t>
+          <t>https://www.indeed.com/viewjob?jk=4a48e7242a74c765</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>Ideas2IT Technology Services</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tennyson, IN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,77 +1571,77 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f9fcd187c753bef</t>
+          <t>https://www.indeed.com/viewjob?jk=3c514f50b938a8dc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
+          <t>Data Engineer- BI Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>Diversified Gas &amp; Oil</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=751a33e38e145115</t>
+          <t>https://www.indeed.com/viewjob?jk=d9cd4d53bb42fc00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Senior Data Scientist</t>
+          <t>Senior Cloud Ops Engineer I - SRE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>CaseWorthy</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,54 +1651,54 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a48e7242a74c765</t>
+          <t>https://www.indeed.com/viewjob?jk=9d69f297c014e4a1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ideas2IT Technology Services</t>
+          <t>Escalent</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tennyson, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c514f50b938a8dc</t>
+          <t>https://www.indeed.com/viewjob?jk=45d62ba2dc0bd875</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer- BI Developer</t>
+          <t>Application Solutions Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Diversified Gas &amp; Oil</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9cd4d53bb42fc00</t>
+          <t>https://www.indeed.com/viewjob?jk=510eace270c01417</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Cloud Ops Engineer I - SRE</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CaseWorthy</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d69f297c014e4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=7481c6f102626c6e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Escalent</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45d62ba2dc0bd875</t>
+          <t>https://www.indeed.com/viewjob?jk=fe69cd7125f7a833</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7481c6f102626c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=c09787e1cb8cb395</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69cd7125f7a833</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4ad7ea1b58a31e</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c09787e1cb8cb395</t>
+          <t>https://www.indeed.com/viewjob?jk=1cc726639aa959a6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Software Development Engineer I - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4ad7ea1b58a31e</t>
+          <t>https://www.indeed.com/viewjob?jk=0b08010c09c91435</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>NextAmp LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,42 +1956,42 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>ECS, RDS, Snowflake, Oracle, SQL Server, Dimensional Modeling, Kimball, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc726639aa959a6</t>
+          <t>https://www.indeed.com/viewjob?jk=112573c8edf11915</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Development Engineer I - ArcGIS Enterprise</t>
+          <t>Sr Engineer, Data &amp; Analytics Platform (Snowflake/dbt)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>RDS, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,59 +2001,59 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b08010c09c91435</t>
+          <t>https://www.indeed.com/viewjob?jk=f401900b912197cd</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NextAmp LLC</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ECS, RDS, Snowflake, Oracle, SQL Server, Dimensional Modeling, Kimball, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=112573c8edf11915</t>
+          <t>https://www.indeed.com/viewjob?jk=f722c5b892610593</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data &amp; Analytics Platform (Snowflake/dbt)</t>
+          <t>Senior Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Value Truck of Arizona</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, Power BI, Tableau, DataOps</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f401900b912197cd</t>
+          <t>https://www.indeed.com/viewjob?jk=49ae49eef7db6241</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f722c5b892610593</t>
+          <t>https://www.indeed.com/viewjob?jk=decf563d2df9d00c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Developer-Full Stack Senior</t>
+          <t>Forward Deployed Engineer - AI SOC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e9f859d9d42bd7</t>
+          <t>https://www.indeed.com/viewjob?jk=29fa83f558965646</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Advanced Software Engineer- Full Stack Cloud Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decf563d2df9d00c</t>
+          <t>https://www.indeed.com/viewjob?jk=78950b770ed7417f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - AI SOC</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>El Toro.com</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fa83f558965646</t>
+          <t>https://www.indeed.com/viewjob?jk=d42d84e2b583adb0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior .NET Developer</t>
+          <t>Senior AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, YARN, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52c472962c791de2</t>
+          <t>https://www.indeed.com/viewjob?jk=0c44bbcac30a87c2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Advanced Software Engineer- Full Stack Cloud Developer</t>
+          <t>Senior AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78950b770ed7417f</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc37b1c10548573</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Quality and Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>El Toro.com</t>
+          <t>Mercedes-Benz Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Vance, AL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42d84e2b583adb0</t>
+          <t>https://www.indeed.com/viewjob?jk=3a36a0ff08797a70</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Engineer</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c44bbcac30a87c2</t>
+          <t>https://www.indeed.com/viewjob?jk=be21268d9d981efd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Engineer</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc37b1c10548573</t>
+          <t>https://www.indeed.com/viewjob?jk=f756de42016efc57</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Quality and Data Engineer</t>
+          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Vance, AL, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a36a0ff08797a70</t>
+          <t>https://www.indeed.com/viewjob?jk=abc756e24b7ebb78</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Senior Snowflake Data Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Redshift, S3, RDS, Scala, Snowflake, DynamoDB, ELT, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be21268d9d981efd</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a8050d86dd2bf8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f756de42016efc57</t>
+          <t>https://www.indeed.com/viewjob?jk=b36c700922532ac2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
+          <t>Azure Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abc756e24b7ebb78</t>
+          <t>https://www.indeed.com/viewjob?jk=32d19f755ee8489a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Platform Engineer (Hybrid)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, Snowflake, DynamoDB, ELT, Splunk, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, PySpark, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a8050d86dd2bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=4223c8030b51f20b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>2026-2027 Information Technology - Software Engineer - Intern</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36c700922532ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=eab14599c79da82b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>2026-2027 Information Technology - Software Engineer - Full-Time</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d19f755ee8489a</t>
+          <t>https://www.indeed.com/viewjob?jk=d6578ea1eb5e5142</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior .NET and SSRS Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, PySpark, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4223c8030b51f20b</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c8883b0dd19abf</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-2027 Information Technology - Software Engineer - Intern</t>
+          <t>Full Stack Developer III - Private Markets Applications</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab14599c79da82b</t>
+          <t>https://www.indeed.com/viewjob?jk=04f2e93224c9a790</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-2027 Information Technology - Software Engineer - Full-Time</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>ThesisGrid</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6578ea1eb5e5142</t>
+          <t>https://www.indeed.com/viewjob?jk=d06761e86ca4aeca</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior .NET and SSRS Developer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c8883b0dd19abf</t>
+          <t>https://www.indeed.com/viewjob?jk=bf57c7d8b4b2d9e4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full Stack Developer III - Private Markets Applications</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f2e93224c9a790</t>
+          <t>https://www.indeed.com/viewjob?jk=032b8db4bfd5e6d8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer 2 (Backend AI)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf57c7d8b4b2d9e4</t>
+          <t>https://www.indeed.com/viewjob?jk=46f856d080d24d05</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032b8db4bfd5e6d8</t>
+          <t>https://www.indeed.com/viewjob?jk=19153bb3202f8519</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f856d080d24d05</t>
+          <t>https://www.indeed.com/viewjob?jk=ee7a2d23cf0b0fbe</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19153bb3202f8519</t>
+          <t>https://www.indeed.com/viewjob?jk=00a3e62df8c707d8</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee7a2d23cf0b0fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=779a1a0a5eccc32e</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3e62df8c707d8</t>
+          <t>https://www.indeed.com/viewjob?jk=8993a2c0de0e70e1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior Software Engineer – Product</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Re:Build Manufacturing</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=779a1a0a5eccc32e</t>
+          <t>https://www.indeed.com/viewjob?jk=61d08f5c56b39289</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Datadrive</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Tableau, DataOps, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8993a2c0de0e70e1</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f20a50010d3a4e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>RPA Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, DataOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fd1f39f284ae52</t>
+          <t>https://www.indeed.com/viewjob?jk=0ebbf24573d559b5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Product</t>
+          <t>Senior UX Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Re:Build Manufacturing</t>
+          <t>Charles River Analytics</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d08f5c56b39289</t>
+          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Specialist, Software Engineer - Test Automation Developer (Ruby &amp; Playwright)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Datadrive</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Tableau, DataOps, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f20a50010d3a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=f00ee1189eddb9b1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Performance Engineer, Information technology</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>ServiceLink</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, DataOps</t>
+          <t>API Gateway, RDS, Azure, Event Hubs, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, AKS</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ebbf24573d559b5</t>
+          <t>https://www.indeed.com/viewjob?jk=f3af50fd888d2a26</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Performance Engineer, Information technology</t>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ServiceLink</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Event Hubs, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, AKS</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3af50fd888d2a26</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb8dc7b4cca4c33</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Specialist, Software Engineer - Test Automation Developer (Ruby &amp; Playwright)</t>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,17 +3286,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins, Git</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f00ee1189eddb9b1</t>
+          <t>https://www.indeed.com/viewjob?jk=a7bee4a1e548e177</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb8dc7b4cca4c33</t>
+          <t>https://www.indeed.com/viewjob?jk=5a54ac0922147b15</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
+          <t>Network/Systems Engineer/DBA</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>CCSI</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, MySQL, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7bee4a1e548e177</t>
+          <t>https://www.indeed.com/viewjob?jk=82f25ac0bbe1b8ca</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
+          <t>Solutions Engineer - Data Visualization</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a54ac0922147b15</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfe4bd64f8f496f</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Network/Systems Engineer/DBA</t>
+          <t>Senior Development Operations Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CCSI</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, MySQL, Splunk, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82f25ac0bbe1b8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=730302ab09184768</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Visualization</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfe4bd64f8f496f</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7fd121bc0e2325</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Appian Dev-Reporting &amp; Analytics</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Department of Finance</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, ETL, Power BI, Tableau, AKS</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88aacc0c7f29344d</t>
+          <t>https://www.indeed.com/viewjob?jk=f41d2b8270473c0a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Development Operations Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git, Azure Monitor, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730302ab09184768</t>
+          <t>https://www.indeed.com/viewjob?jk=8a6494cda8c81441</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7fd121bc0e2325</t>
+          <t>https://www.indeed.com/viewjob?jk=e7dbdf6ce237b13d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Verisure</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Uniontown, OH, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, SQL Server, REST API integration, Power BI, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f41d2b8270473c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=c374eb71cdd5829a</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Asurion</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,120 +3636,15 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, AWS CodePipeline, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a6494cda8c81441</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Junior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Aivra Health</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7dbdf6ce237b13d</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Verisure</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Uniontown, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, SQL Server, REST API integration, Power BI, CI/CD, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c374eb71cdd5829a</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Asurion</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, AWS CodePipeline, Docker</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b4a35189b0c83845</t>
         </is>

--- a/results/job_matches_2026-07-15.xlsx
+++ b/results/job_matches_2026-07-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure Data Architect</t>
+          <t>Azure Data -AI -Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -923,60 +923,60 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Senior Data Scientist - Artificial Intelligence</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Itero Group</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e304be37d5897728</t>
+          <t>https://www.indeed.com/viewjob?jk=7cf8977f54a3cd6f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Engineer</t>
+          <t>Senior Cloud Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Itero Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Kimball, Star Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9724f20b3e8cf9d3</t>
+          <t>https://www.indeed.com/viewjob?jk=0426c9944a6312e8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Management Professional - Data Engineering - Entities</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,172 +1021,172 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a24491194c9938</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f5d11d7b626cfc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Artificial Intelligence</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cf8977f54a3cd6f</t>
+          <t>https://www.indeed.com/viewjob?jk=a407a20c56f80680</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Remote</t>
+          <t>FinOps Engineer (contract)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0426c9944a6312e8</t>
+          <t>https://www.indeed.com/viewjob?jk=ba947e467674b693</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f5d11d7b626cfc</t>
+          <t>https://www.indeed.com/viewjob?jk=9690379ea46f2be7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Moffitt Cancer Center</t>
+          <t>Berkley</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, dbt, MLflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a407a20c56f80680</t>
+          <t>https://www.indeed.com/viewjob?jk=7656191539f10c8f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Native Developer- Europe</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>GE Appliances</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=444a0e6bd539f82b</t>
+          <t>https://www.indeed.com/viewjob?jk=f488fb42bdd9a3e5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Native Builder-Europe</t>
+          <t>Senior Solutions Architect - Airflow (West Coast)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae934e8451ebc14c</t>
+          <t>https://www.indeed.com/viewjob?jk=563d41613641e2d6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>JBoss Apache Fuse Engineer with Healthcare (RCM)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Berkley</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,77 +1256,77 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, dbt, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7656191539f10c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=bdef99a180f7357d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Full Stack Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9690379ea46f2be7</t>
+          <t>https://www.indeed.com/viewjob?jk=e643625eb77abd14</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>DataHub Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GE Appliances</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, S3, IAM, RDS, Azure, Kafka, Kafka Connect, Oracle, MySQL, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,59 +1336,59 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f488fb42bdd9a3e5</t>
+          <t>https://www.indeed.com/viewjob?jk=5423277344900438</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (West Coast)</t>
+          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563d41613641e2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=4f9fcd187c753bef</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AWS Full Stack Engineer</t>
+          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e643625eb77abd14</t>
+          <t>https://www.indeed.com/viewjob?jk=751a33e38e145115</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DataHub Developer</t>
+          <t>Technical Solution Architect - Salesforce Service Cloud</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>IT Shoulders, Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Kafka, Kafka Connect, Oracle, MySQL, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5423277344900438</t>
+          <t>https://www.indeed.com/viewjob?jk=6285bc228bba1070</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
+          <t>Solutions Architect (RICHMOND, VA, US, 23219)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>Dominion Energy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f9fcd187c753bef</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe9bd2b5131f29d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
+          <t>Artificial Intelligence Senior Data Scientist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=751a33e38e145115</t>
+          <t>https://www.indeed.com/viewjob?jk=4a48e7242a74c765</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Senior Data Scientist</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>Ideas2IT Technology Services</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tennyson, IN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,42 +1536,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a48e7242a74c765</t>
+          <t>https://www.indeed.com/viewjob?jk=3c514f50b938a8dc</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ideas2IT Technology Services</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tennyson, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c514f50b938a8dc</t>
+          <t>https://www.indeed.com/viewjob?jk=5df64a9e9d059759</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Knowledge Graph Engineer/Semantic Web Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Escalent</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45d62ba2dc0bd875</t>
+          <t>https://www.indeed.com/viewjob?jk=f1326954160b9d00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Application Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=510eace270c01417</t>
+          <t>https://www.indeed.com/viewjob?jk=7481c6f102626c6e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Application Solutions Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7481c6f102626c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=510eace270c01417</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Software Development Engineer I - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe69cd7125f7a833</t>
+          <t>https://www.indeed.com/viewjob?jk=0b08010c09c91435</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>NextAmp LLC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,42 +1816,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>ECS, RDS, Snowflake, Oracle, SQL Server, Dimensional Modeling, Kimball, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c09787e1cb8cb395</t>
+          <t>https://www.indeed.com/viewjob?jk=112573c8edf11915</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Sr Engineer, Data &amp; Analytics Platform (Snowflake/dbt)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>RDS, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,129 +1861,129 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4ad7ea1b58a31e</t>
+          <t>https://www.indeed.com/viewjob?jk=f401900b912197cd</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc726639aa959a6</t>
+          <t>https://www.indeed.com/viewjob?jk=f722c5b892610593</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Development Engineer I - ArcGIS Enterprise</t>
+          <t>API/Microservices/AWS Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b08010c09c91435</t>
+          <t>https://www.indeed.com/viewjob?jk=d840931b85553d6b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NextAmp LLC</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ECS, RDS, Snowflake, Oracle, SQL Server, Dimensional Modeling, Kimball, Star Schema, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=112573c8edf11915</t>
+          <t>https://www.indeed.com/viewjob?jk=decf563d2df9d00c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data &amp; Analytics Platform (Snowflake/dbt)</t>
+          <t>Advanced Software Engineer- Full Stack Cloud Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, Power BI, Tableau, DataOps</t>
+          <t>AWS, S3, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f401900b912197cd</t>
+          <t>https://www.indeed.com/viewjob?jk=78950b770ed7417f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>El Toro.com</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f722c5b892610593</t>
+          <t>https://www.indeed.com/viewjob?jk=d42d84e2b583adb0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Analyst</t>
+          <t>Forward Deployed Engineer - AI SOC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Value Truck of Arizona</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49ae49eef7db6241</t>
+          <t>https://www.indeed.com/viewjob?jk=29fa83f558965646</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Senior AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decf563d2df9d00c</t>
+          <t>https://www.indeed.com/viewjob?jk=0c44bbcac30a87c2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - AI SOC</t>
+          <t>Senior AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fa83f558965646</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc37b1c10548573</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Advanced Software Engineer- Full Stack Cloud Developer</t>
+          <t>Quality and Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Mercedes-Benz Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Vance, AL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78950b770ed7417f</t>
+          <t>https://www.indeed.com/viewjob?jk=3a36a0ff08797a70</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior DevOps/MLOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>El Toro.com</t>
+          <t>Leverege</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42d84e2b583adb0</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2c5ef617a021a1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Engineer</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c44bbcac30a87c2</t>
+          <t>https://www.indeed.com/viewjob?jk=be21268d9d981efd</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Engineer</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc37b1c10548573</t>
+          <t>https://www.indeed.com/viewjob?jk=f756de42016efc57</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Quality and Data Engineer</t>
+          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Vance, AL, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a36a0ff08797a70</t>
+          <t>https://www.indeed.com/viewjob?jk=abc756e24b7ebb78</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Senior Snowflake Data Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Redshift, S3, RDS, Scala, Snowflake, DynamoDB, ELT, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be21268d9d981efd</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a8050d86dd2bf8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f756de42016efc57</t>
+          <t>https://www.indeed.com/viewjob?jk=b36c700922532ac2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
+          <t>Azure Platform Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abc756e24b7ebb78</t>
+          <t>https://www.indeed.com/viewjob?jk=32d19f755ee8489a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Platform Engineer (Hybrid)</t>
+          <t>2026-2027 Information Technology - Software Engineer - Intern</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, Snowflake, DynamoDB, ELT, Splunk, MLflow</t>
+          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a8050d86dd2bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=eab14599c79da82b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>2026-2027 Information Technology - Software Engineer - Full-Time</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36c700922532ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=d6578ea1eb5e5142</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>Senior .NET and SSRS Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d19f755ee8489a</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c8883b0dd19abf</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ThesisGrid</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, PySpark, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4223c8030b51f20b</t>
+          <t>https://www.indeed.com/viewjob?jk=d06761e86ca4aeca</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-2027 Information Technology - Software Engineer - Intern</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab14599c79da82b</t>
+          <t>https://www.indeed.com/viewjob?jk=bf57c7d8b4b2d9e4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-2027 Information Technology - Software Engineer - Full-Time</t>
+          <t>Semantic Web Engineer or knowledge graph Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>MagicForce</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,42 +2621,42 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6578ea1eb5e5142</t>
+          <t>https://www.indeed.com/viewjob?jk=d42f448146cc2551</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior .NET and SSRS Developer</t>
+          <t>Senior Software Engineer – Product</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Re:Build Manufacturing</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c8883b0dd19abf</t>
+          <t>https://www.indeed.com/viewjob?jk=61d08f5c56b39289</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full Stack Developer III - Private Markets Applications</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Datadrive</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Tableau, DataOps, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,172 +2701,172 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f2e93224c9a790</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f20a50010d3a4e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ThesisGrid</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, DataOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d06761e86ca4aeca</t>
+          <t>https://www.indeed.com/viewjob?jk=0ebbf24573d559b5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Business Intelligence Analyst I - REMOTE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Net Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Redshift, RDS, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf57c7d8b4b2d9e4</t>
+          <t>https://www.indeed.com/viewjob?jk=2050bd296e3aa9f7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior UX Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Charles River Analytics</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032b8db4bfd5e6d8</t>
+          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Specialist, Software Engineer - Test Automation Developer (Ruby &amp; Playwright)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f856d080d24d05</t>
+          <t>https://www.indeed.com/viewjob?jk=f00ee1189eddb9b1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Performance Engineer, Information technology</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>ServiceLink</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Event Hubs, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, AKS</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,137 +2876,137 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19153bb3202f8519</t>
+          <t>https://www.indeed.com/viewjob?jk=f3af50fd888d2a26</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee7a2d23cf0b0fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb8dc7b4cca4c33</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00a3e62df8c707d8</t>
+          <t>https://www.indeed.com/viewjob?jk=a7bee4a1e548e177</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=779a1a0a5eccc32e</t>
+          <t>https://www.indeed.com/viewjob?jk=5a54ac0922147b15</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Backend AI)</t>
+          <t>Senior Development Operations Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8993a2c0de0e70e1</t>
+          <t>https://www.indeed.com/viewjob?jk=730302ab09184768</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Product</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Re:Build Manufacturing</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d08f5c56b39289</t>
+          <t>https://www.indeed.com/viewjob?jk=3e7fd121bc0e2325</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Datadrive</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Tableau, DataOps, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f20a50010d3a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=f41d2b8270473c0a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, DataOps</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ebbf24573d559b5</t>
+          <t>https://www.indeed.com/viewjob?jk=8a6494cda8c81441</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,507 +3146,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Specialist, Software Engineer - Test Automation Developer (Ruby &amp; Playwright)</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Nationwide Mutual Insurance Company</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f00ee1189eddb9b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Performance Engineer, Information technology</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>ServiceLink</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Azure, Event Hubs, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, AKS</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f3af50fd888d2a26</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>VetsEZ</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb8dc7b4cca4c33</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>VetsEZ</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a7bee4a1e548e177</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>VetsEZ</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a54ac0922147b15</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Network/Systems Engineer/DBA</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>CCSI</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, MySQL, Splunk, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=82f25ac0bbe1b8ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Solutions Engineer - Data Visualization</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>SHI International</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling, Dimensional Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfe4bd64f8f496f</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior Development Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>TTX</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git, Azure Monitor, Python</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=730302ab09184768</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7fd121bc0e2325</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f41d2b8270473c0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a6494cda8c81441</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Junior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Aivra Health</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=e7dbdf6ce237b13d</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Verisure</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Uniontown, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, SQL Server, REST API integration, Power BI, CI/CD, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c374eb71cdd5829a</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Software Engineer 2 - Internal Development Platform (IDP)</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Asurion</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, AWS CodePipeline, Docker</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a35189b0c83845</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-15.xlsx
+++ b/results/job_matches_2026-07-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3720530c1ac33814</t>
+          <t>https://www.indeed.com/viewjob?jk=a77df08519b290c1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer III - Glue/Python/Pyspark</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bd064010356a824</t>
+          <t>https://www.indeed.com/viewjob?jk=3720530c1ac33814</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Software Engineer III - Glue/Python/Pyspark</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,94 +881,94 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9be95a71934961d</t>
+          <t>https://www.indeed.com/viewjob?jk=0bd064010356a824</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Senior Data Scientist - Artificial Intelligence</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Modivcare</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf05ce3284e6a20</t>
+          <t>https://www.indeed.com/viewjob?jk=7cf8977f54a3cd6f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Artificial Intelligence</t>
+          <t>Senior Cloud Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cf8977f54a3cd6f</t>
+          <t>https://www.indeed.com/viewjob?jk=0426c9944a6312e8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0426c9944a6312e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f5d11d7b626cfc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,69 +1011,69 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f5d11d7b626cfc</t>
+          <t>https://www.indeed.com/viewjob?jk=a407a20c56f80680</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>FinOps Engineer (contract)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Moffitt Cancer Center</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a407a20c56f80680</t>
+          <t>https://www.indeed.com/viewjob?jk=ba947e467674b693</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FinOps Engineer (contract)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba947e467674b693</t>
+          <t>https://www.indeed.com/viewjob?jk=9690379ea46f2be7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Berkley</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, dbt, MLflow</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9690379ea46f2be7</t>
+          <t>https://www.indeed.com/viewjob?jk=7656191539f10c8f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Berkley</t>
+          <t>GE Appliances</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, dbt, MLflow</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7656191539f10c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=f488fb42bdd9a3e5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Solutions Architect - Airflow (West Coast)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GE Appliances</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f488fb42bdd9a3e5</t>
+          <t>https://www.indeed.com/viewjob?jk=563d41613641e2d6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (West Coast)</t>
+          <t>JBoss Apache Fuse Engineer with Healthcare (RCM)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,29 +1221,29 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563d41613641e2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=bdef99a180f7357d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JBoss Apache Fuse Engineer with Healthcare (RCM)</t>
+          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1252,38 +1252,38 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdef99a180f7357d</t>
+          <t>https://www.indeed.com/viewjob?jk=4f9fcd187c753bef</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS Full Stack Engineer</t>
+          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e643625eb77abd14</t>
+          <t>https://www.indeed.com/viewjob?jk=751a33e38e145115</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DataHub Developer</t>
+          <t>Technical Solution Architect - Salesforce Service Cloud</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>IT Shoulders, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Kafka, Kafka Connect, Oracle, MySQL, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5423277344900438</t>
+          <t>https://www.indeed.com/viewjob?jk=6285bc228bba1070</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
+          <t>Solutions Architect (RICHMOND, VA, US, 23219)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>Dominion Energy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f9fcd187c753bef</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe9bd2b5131f29d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
+          <t>Artificial Intelligence Senior Data Scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=751a33e38e145115</t>
+          <t>https://www.indeed.com/viewjob?jk=4a48e7242a74c765</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Technical Solution Architect - Salesforce Service Cloud</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IT Shoulders, Inc.</t>
+          <t>Ideas2IT Technology Services</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Tennyson, IN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6285bc228bba1070</t>
+          <t>https://www.indeed.com/viewjob?jk=3c514f50b938a8dc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Solutions Architect (RICHMOND, VA, US, 23219)</t>
+          <t>Full Stack Engineer, Data Services</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Star Schema, Snowflake Schema</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,94 +1476,94 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe9bd2b5131f29d</t>
+          <t>https://www.indeed.com/viewjob?jk=adcff14ee1b8e664</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Senior Data Scientist</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a48e7242a74c765</t>
+          <t>https://www.indeed.com/viewjob?jk=5df64a9e9d059759</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Data Engineer- BI Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ideas2IT Technology Services</t>
+          <t>Diversified Gas &amp; Oil</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tennyson, IN, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c514f50b938a8dc</t>
+          <t>https://www.indeed.com/viewjob?jk=d9cd4d53bb42fc00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Senior Cloud Ops Engineer I - SRE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>CaseWorthy</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5df64a9e9d059759</t>
+          <t>https://www.indeed.com/viewjob?jk=9d69f297c014e4a1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer- BI Developer</t>
+          <t>Knowledge Graph Engineer/Semantic Web Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Diversified Gas &amp; Oil</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9cd4d53bb42fc00</t>
+          <t>https://www.indeed.com/viewjob?jk=f1326954160b9d00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Cloud Ops Engineer I - SRE</t>
+          <t>Application Solutions Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CaseWorthy</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d69f297c014e4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=510eace270c01417</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Knowledge Graph Engineer/Semantic Web Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1326954160b9d00</t>
+          <t>https://www.indeed.com/viewjob?jk=7481c6f102626c6e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer I - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7481c6f102626c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=0b08010c09c91435</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Application Solutions Architect</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>NextAmp LLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,42 +1746,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>ECS, RDS, Snowflake, Oracle, SQL Server, Dimensional Modeling, Kimball, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=510eace270c01417</t>
+          <t>https://www.indeed.com/viewjob?jk=112573c8edf11915</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Development Engineer I - ArcGIS Enterprise</t>
+          <t>Sr Engineer, Data &amp; Analytics Platform (Snowflake/dbt)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>RDS, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,59 +1791,59 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b08010c09c91435</t>
+          <t>https://www.indeed.com/viewjob?jk=f401900b912197cd</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NextAmp LLC</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ECS, RDS, Snowflake, Oracle, SQL Server, Dimensional Modeling, Kimball, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=112573c8edf11915</t>
+          <t>https://www.indeed.com/viewjob?jk=f722c5b892610593</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data &amp; Analytics Platform (Snowflake/dbt)</t>
+          <t>API/Microservices/AWS Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, Power BI, Tableau, DataOps</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f401900b912197cd</t>
+          <t>https://www.indeed.com/viewjob?jk=d840931b85553d6b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f722c5b892610593</t>
+          <t>https://www.indeed.com/viewjob?jk=decf563d2df9d00c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>API/Microservices/AWS Software Engineer - Remote</t>
+          <t>Advanced Software Engineer- Full Stack Cloud Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d840931b85553d6b</t>
+          <t>https://www.indeed.com/viewjob?jk=78950b770ed7417f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Forward Deployed Engineer - AI SOC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decf563d2df9d00c</t>
+          <t>https://www.indeed.com/viewjob?jk=29fa83f558965646</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Advanced Software Engineer- Full Stack Cloud Developer</t>
+          <t>Senior AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78950b770ed7417f</t>
+          <t>https://www.indeed.com/viewjob?jk=0c44bbcac30a87c2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>El Toro.com</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42d84e2b583adb0</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc37b1c10548573</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - AI SOC</t>
+          <t>Quality and Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Mercedes-Benz Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vance, AL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,94 +2071,94 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fa83f558965646</t>
+          <t>https://www.indeed.com/viewjob?jk=3a36a0ff08797a70</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>Mass General Brigham</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c44bbcac30a87c2</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a26b0635f31911</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Engineer</t>
+          <t>Senior DevOps/MLOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>Leverege</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc37b1c10548573</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2c5ef617a021a1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Quality and Data Engineer</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Vance, AL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a36a0ff08797a70</t>
+          <t>https://www.indeed.com/viewjob?jk=be21268d9d981efd</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior DevOps/MLOps Engineer</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Leverege</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2c5ef617a021a1</t>
+          <t>https://www.indeed.com/viewjob?jk=f756de42016efc57</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be21268d9d981efd</t>
+          <t>https://www.indeed.com/viewjob?jk=abc756e24b7ebb78</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Senior Snowflake Data Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Redshift, S3, RDS, Scala, Snowflake, DynamoDB, ELT, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f756de42016efc57</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a8050d86dd2bf8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abc756e24b7ebb78</t>
+          <t>https://www.indeed.com/viewjob?jk=b36c700922532ac2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Platform Engineer (Hybrid)</t>
+          <t>Azure Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, Snowflake, DynamoDB, ELT, Splunk, MLflow</t>
+          <t>RDS, Azure, Data Factory, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a8050d86dd2bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=32d19f755ee8489a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>AWS Full Stack Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36c700922532ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=4e284c3a4db13c5e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>2026-2027 Information Technology - Software Engineer - Intern</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,14 +2421,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d19f755ee8489a</t>
+          <t>https://www.indeed.com/viewjob?jk=eab14599c79da82b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-2027 Information Technology - Software Engineer - Intern</t>
+          <t>2026-2027 Information Technology - Software Engineer - Full-Time</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab14599c79da82b</t>
+          <t>https://www.indeed.com/viewjob?jk=d6578ea1eb5e5142</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-2027 Information Technology - Software Engineer - Full-Time</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>ThesisGrid</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6578ea1eb5e5142</t>
+          <t>https://www.indeed.com/viewjob?jk=d06761e86ca4aeca</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior .NET and SSRS Developer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c8883b0dd19abf</t>
+          <t>https://www.indeed.com/viewjob?jk=bf57c7d8b4b2d9e4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Semantic Web Engineer or knowledge graph Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ThesisGrid</t>
+          <t>MagicForce</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d06761e86ca4aeca</t>
+          <t>https://www.indeed.com/viewjob?jk=d42f448146cc2551</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer – Product</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Re:Build Manufacturing</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf57c7d8b4b2d9e4</t>
+          <t>https://www.indeed.com/viewjob?jk=61d08f5c56b39289</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Semantic Web Engineer or knowledge graph Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MagicForce</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
+          <t>AWS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42f448146cc2551</t>
+          <t>https://www.indeed.com/viewjob?jk=b121c03b7571c591</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Product</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Re:Build Manufacturing</t>
+          <t>Datadrive</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Tableau, DataOps, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d08f5c56b39289</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f20a50010d3a4e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Datadrive</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Tableau, DataOps, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, DataOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f20a50010d3a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=0ebbf24573d559b5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Intelligence Analyst I - REMOTE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Net Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, DataOps</t>
+          <t>AWS, Redshift, RDS, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ebbf24573d559b5</t>
+          <t>https://www.indeed.com/viewjob?jk=2050bd296e3aa9f7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst I - REMOTE</t>
+          <t>Senior UX Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Net Health</t>
+          <t>Charles River Analytics</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, dbt, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2050bd296e3aa9f7</t>
+          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>Avid Technology</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
+          <t>https://www.indeed.com/viewjob?jk=42278e3835861af7</t>
         </is>
       </c>
     </row>
@@ -3157,6 +3157,41 @@
       <c r="G78" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e7dbdf6ce237b13d</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>VINMAR INTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43aa1a5e37a0ff4a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-15.xlsx
+++ b/results/job_matches_2026-07-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,35 +503,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hanover, NH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b192e5946ee2ce27</t>
+          <t>https://www.indeed.com/viewjob?jk=1faf9fe4c0bcd7c6</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c17e2e00004cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=b192e5946ee2ce27</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d9682d5f343e62</t>
+          <t>https://www.indeed.com/viewjob?jk=93c17e2e00004cf8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure Data -AI -Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c9310d05771935</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d9682d5f343e62</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Junior Architect / Senior Data Engineer - Remote</t>
+          <t>Azure Data -AI -Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e53a2ba6f9a4021</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c9310d05771935</t>
         </is>
       </c>
     </row>
@@ -748,35 +748,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data AI Architect</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>Axiomatic AI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, Photon, GCP, Vertex AI, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9de5ac8d42dd8ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=675661d633a7ce19</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Artificial Intelligence</t>
+          <t>Data Platform Engineer (Data 360)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,52 +906,52 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Google Cloud Platform, Vertex AI, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cf8977f54a3cd6f</t>
+          <t>https://www.indeed.com/viewjob?jk=25f44870043020f2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Remote</t>
+          <t>Senior Data Scientist - Artificial Intelligence</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0426c9944a6312e8</t>
+          <t>https://www.indeed.com/viewjob?jk=7cf8977f54a3cd6f</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer - AI Platforms and Automation</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Intelligent Medical Objects</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, PostgreSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9690379ea46f2be7</t>
+          <t>https://www.indeed.com/viewjob?jk=60174baa1f0aad14</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (West Coast)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563d41613641e2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=9690379ea46f2be7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JBoss Apache Fuse Engineer with Healthcare (RCM)</t>
+          <t>Senior Solutions Architect - Airflow (West Coast)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,29 +1221,29 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdef99a180f7357d</t>
+          <t>https://www.indeed.com/viewjob?jk=563d41613641e2d6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
+          <t>JBoss Apache Fuse Engineer with Healthcare (RCM)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1252,21 +1252,21 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f9fcd187c753bef</t>
+          <t>https://www.indeed.com/viewjob?jk=bdef99a180f7357d</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=751a33e38e145115</t>
+          <t>https://www.indeed.com/viewjob?jk=4f9fcd187c753bef</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Technical Solution Architect - Salesforce Service Cloud</t>
+          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IT Shoulders, Inc.</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6285bc228bba1070</t>
+          <t>https://www.indeed.com/viewjob?jk=751a33e38e145115</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Solutions Architect (RICHMOND, VA, US, 23219)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>Moderna</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Star Schema, Snowflake Schema</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe9bd2b5131f29d</t>
+          <t>https://www.indeed.com/viewjob?jk=d9727f7b8e7ba49f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Senior Data Scientist</t>
+          <t>Technical Solution Architect - Salesforce Service Cloud</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>IT Shoulders, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a48e7242a74c765</t>
+          <t>https://www.indeed.com/viewjob?jk=6285bc228bba1070</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Solutions Architect (RICHMOND, VA, US, 23219)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ideas2IT Technology Services</t>
+          <t>Dominion Energy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tennyson, IN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c514f50b938a8dc</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe9bd2b5131f29d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Data Services</t>
+          <t>Artificial Intelligence Senior Data Scientist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcff14ee1b8e664</t>
+          <t>https://www.indeed.com/viewjob?jk=4a48e7242a74c765</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Full Stack Engineer, Data Services</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,59 +1511,59 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5df64a9e9d059759</t>
+          <t>https://www.indeed.com/viewjob?jk=adcff14ee1b8e664</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer- BI Developer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Diversified Gas &amp; Oil</t>
+          <t>Ideas2IT Technology Services</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Tennyson, IN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9cd4d53bb42fc00</t>
+          <t>https://www.indeed.com/viewjob?jk=3c514f50b938a8dc</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Cloud Ops Engineer I - SRE</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CaseWorthy</t>
+          <t>Fieldwire</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,29 +1571,29 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d69f297c014e4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=52528f466514c758</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Knowledge Graph Engineer/Semantic Web Engineer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,19 +1616,19 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1326954160b9d00</t>
+          <t>https://www.indeed.com/viewjob?jk=5df64a9e9d059759</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Application Solutions Architect</t>
+          <t>Data Engineer- BI Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>Diversified Gas &amp; Oil</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=510eace270c01417</t>
+          <t>https://www.indeed.com/viewjob?jk=d9cd4d53bb42fc00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Ops Engineer I - SRE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>CaseWorthy</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7481c6f102626c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=9d69f297c014e4a1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Development Engineer I - ArcGIS Enterprise</t>
+          <t>Application Solutions Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b08010c09c91435</t>
+          <t>https://www.indeed.com/viewjob?jk=510eace270c01417</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Knowledge Graph Engineer/Semantic Web Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NextAmp LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ECS, RDS, Snowflake, Oracle, SQL Server, Dimensional Modeling, Kimball, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,164 +1756,164 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=112573c8edf11915</t>
+          <t>https://www.indeed.com/viewjob?jk=f1326954160b9d00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data &amp; Analytics Platform (Snowflake/dbt)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, Power BI, Tableau, DataOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f401900b912197cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e9074111e1ca6eb3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f722c5b892610593</t>
+          <t>https://www.indeed.com/viewjob?jk=7481c6f102626c6e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>API/Microservices/AWS Software Engineer - Remote</t>
+          <t>Software Development Engineer I - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d840931b85553d6b</t>
+          <t>https://www.indeed.com/viewjob?jk=0b08010c09c91435</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>NextAmp LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>ECS, RDS, Snowflake, Oracle, SQL Server, Dimensional Modeling, Kimball, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decf563d2df9d00c</t>
+          <t>https://www.indeed.com/viewjob?jk=112573c8edf11915</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Advanced Software Engineer- Full Stack Cloud Developer</t>
+          <t>Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>CONNEXUS CREDIT UNION</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78950b770ed7417f</t>
+          <t>https://www.indeed.com/viewjob?jk=17489ce3b83eeabe</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - AI SOC</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fa83f558965646</t>
+          <t>https://www.indeed.com/viewjob?jk=f722c5b892610593</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Engineer</t>
+          <t>Sr Engineer, Data &amp; Analytics Platform (Snowflake/dbt)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, Power BI, Tableau, DataOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c44bbcac30a87c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f401900b912197cd</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Engineer</t>
+          <t>Data Engineer - Business Analytics</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,77 +2026,77 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc37b1c10548573</t>
+          <t>https://www.indeed.com/viewjob?jk=33816acdbf998550</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Quality and Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Vance, AL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a36a0ff08797a70</t>
+          <t>https://www.indeed.com/viewjob?jk=6e899285a709ae99</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mass General Brigham</t>
+          <t>Biztec Global</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a26b0635f31911</t>
+          <t>https://www.indeed.com/viewjob?jk=f1dd7af4bac5667f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior DevOps/MLOps Engineer</t>
+          <t>API/Microservices/AWS Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Leverege</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2c5ef617a021a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d840931b85553d6b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be21268d9d981efd</t>
+          <t>https://www.indeed.com/viewjob?jk=decf563d2df9d00c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Advanced Software Engineer- Full Stack Cloud Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, S3, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f756de42016efc57</t>
+          <t>https://www.indeed.com/viewjob?jk=78950b770ed7417f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
+          <t>Forward Deployed Engineer - AI SOC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abc756e24b7ebb78</t>
+          <t>https://www.indeed.com/viewjob?jk=29fa83f558965646</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Platform Engineer (Hybrid)</t>
+          <t>Senior AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, Snowflake, DynamoDB, ELT, Splunk, MLflow</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a8050d86dd2bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=0c44bbcac30a87c2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Senior AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36c700922532ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc37b1c10548573</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Mass General Brigham</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d19f755ee8489a</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a26b0635f31911</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AWS Full Stack Developer</t>
+          <t>Senior DevOps/MLOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>Leverege</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, Scala, DynamoDB</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e284c3a4db13c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2c5ef617a021a1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-2027 Information Technology - Software Engineer - Intern</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab14599c79da82b</t>
+          <t>https://www.indeed.com/viewjob?jk=be21268d9d981efd</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-2027 Information Technology - Software Engineer - Full-Time</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6578ea1eb5e5142</t>
+          <t>https://www.indeed.com/viewjob?jk=f756de42016efc57</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ThesisGrid</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d06761e86ca4aeca</t>
+          <t>https://www.indeed.com/viewjob?jk=abc756e24b7ebb78</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Snowflake Data Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, Scala, Snowflake, DynamoDB, ELT, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf57c7d8b4b2d9e4</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a8050d86dd2bf8</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Semantic Web Engineer or knowledge graph Engineer</t>
+          <t>Quality and Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MagicForce</t>
+          <t>Mercedes-Benz Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vance, AL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,42 +2551,42 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42f448146cc2551</t>
+          <t>https://www.indeed.com/viewjob?jk=3a36a0ff08797a70</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Product</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Re:Build Manufacturing</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,172 +2596,172 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d08f5c56b39289</t>
+          <t>https://www.indeed.com/viewjob?jk=b36c700922532ac2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Azure Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>RDS, Azure, Data Factory, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b121c03b7571c591</t>
+          <t>https://www.indeed.com/viewjob?jk=32d19f755ee8489a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AWS Full Stack Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Datadrive</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Tableau, DataOps, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f20a50010d3a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=4e284c3a4db13c5e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>ThesisGrid</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, DataOps</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ebbf24573d559b5</t>
+          <t>https://www.indeed.com/viewjob?jk=d06761e86ca4aeca</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst I - REMOTE</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Net Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2050bd296e3aa9f7</t>
+          <t>https://www.indeed.com/viewjob?jk=bf57c7d8b4b2d9e4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer</t>
+          <t>Semantic Web Engineer or knowledge graph Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>MagicForce</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, RDS, Azure, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
+          <t>https://www.indeed.com/viewjob?jk=d42f448146cc2551</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Avid Technology</t>
+          <t>Biztec Global</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42278e3835861af7</t>
+          <t>https://www.indeed.com/viewjob?jk=34d1cfa7ddeeb193</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Specialist, Software Engineer - Test Automation Developer (Ruby &amp; Playwright)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f00ee1189eddb9b1</t>
+          <t>https://www.indeed.com/viewjob?jk=b121c03b7571c591</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Performance Engineer, Information technology</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ServiceLink</t>
+          <t>Datadrive</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Event Hubs, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, AKS</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Tableau, DataOps, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3af50fd888d2a26</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f20a50010d3a4e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, DataOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb8dc7b4cca4c33</t>
+          <t>https://www.indeed.com/viewjob?jk=0ebbf24573d559b5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
+          <t>Senior Software Engineer – Product</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>Re:Build Manufacturing</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7bee4a1e548e177</t>
+          <t>https://www.indeed.com/viewjob?jk=61d08f5c56b39289</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
+          <t>AWS Devops - AOM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a54ac0922147b15</t>
+          <t>https://www.indeed.com/viewjob?jk=fe4c170529e0e9c9</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Development Operations Engineer</t>
+          <t>Senior AWS Software Engineer (Integrations Team)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>City IT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Marshfield, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git, Azure Monitor, Python</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730302ab09184768</t>
+          <t>https://www.indeed.com/viewjob?jk=4a82bf3693f26a75</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior AWS Software Engineer (Integrations Team)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>City IT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7fd121bc0e2325</t>
+          <t>https://www.indeed.com/viewjob?jk=948d5244cfe1a3f8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Avid Technology</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f41d2b8270473c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=42278e3835861af7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior UX Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Charles River Analytics</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a6494cda8c81441</t>
+          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Specialist, Software Engineer - Test Automation Developer (Ruby &amp; Playwright)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7dbdf6ce237b13d</t>
+          <t>https://www.indeed.com/viewjob?jk=f00ee1189eddb9b1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Performance Engineer, Information technology</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>VINMAR INTERNATIONAL</t>
+          <t>ServiceLink</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,15 +3181,330 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
+          <t>API Gateway, RDS, Azure, Event Hubs, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, AKS</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3af50fd888d2a26</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>VetsEZ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eeb8dc7b4cca4c33</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>VetsEZ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7bee4a1e548e177</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>VetsEZ</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a54ac0922147b15</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Business Intelligence Analyst I - REMOTE</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Net Health</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2050bd296e3aa9f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior Development Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>TTX</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git, Azure Monitor, Python</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=730302ab09184768</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e7fd121bc0e2325</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f41d2b8270473c0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a6494cda8c81441</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>VINMAR INTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>AWS, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, Docker</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=43aa1a5e37a0ff4a</t>
         </is>

--- a/results/job_matches_2026-07-15.xlsx
+++ b/results/job_matches_2026-07-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Omada Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>25.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, SQS, SNS, Databricks, BigQuery, Spark</t>
+          <t>AWS, Lambda, Redshift, IAM, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0663114dfd06c9eb</t>
+          <t>https://www.indeed.com/viewjob?jk=bd9e10d0ccdb5375</t>
         </is>
       </c>
     </row>
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Data -AI -Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b192e5946ee2ce27</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c9310d05771935</t>
         </is>
       </c>
     </row>
@@ -578,55 +578,55 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>AEM Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.8</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c17e2e00004cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=cb427fa873ed5fed</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer Remote - US • Remote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Daxko</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.8</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Athena, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d9682d5f343e62</t>
+          <t>https://www.indeed.com/viewjob?jk=d212feaf575e2588</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Azure Data -AI -Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Daxko</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.8</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Athena, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,102 +671,102 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c9310d05771935</t>
+          <t>https://www.indeed.com/viewjob?jk=419f9c53a083aba9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Remote - US • Remote</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Daxko</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Athena, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d212feaf575e2588</t>
+          <t>https://www.indeed.com/viewjob?jk=a77df08519b290c1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Daxko</t>
+          <t>Axiomatic AI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Athena, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, API Gateway, RDS, Azure, Photon, GCP, Vertex AI, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=419f9c53a083aba9</t>
+          <t>https://www.indeed.com/viewjob?jk=675661d633a7ce19</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Platform Engineer (Data 360)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Axiomatic AI</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Photon, GCP, Vertex AI, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Google Cloud Platform, Vertex AI, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,269 +776,269 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675661d633a7ce19</t>
+          <t>https://www.indeed.com/viewjob?jk=25f44870043020f2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Scientist - Artificial Intelligence</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77df08519b290c1</t>
+          <t>https://www.indeed.com/viewjob?jk=7cf8977f54a3cd6f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Solutions Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Menasha, WI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, SQL Server, Cassandra, NoSQL, Data Modeling</t>
+          <t>Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3720530c1ac33814</t>
+          <t>https://www.indeed.com/viewjob?jk=a104f9a2c71e1bcc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer III - Glue/Python/Pyspark</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Menasha, WI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bd064010356a824</t>
+          <t>https://www.indeed.com/viewjob?jk=dd5be7395930eac9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Data 360)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Google Cloud Platform, Vertex AI, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f44870043020f2</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f5d11d7b626cfc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Artificial Intelligence</t>
+          <t>FinOps Engineer (contract)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cf8977f54a3cd6f</t>
+          <t>https://www.indeed.com/viewjob?jk=ba947e467674b693</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f5d11d7b626cfc</t>
+          <t>https://www.indeed.com/viewjob?jk=d20671f1ab98e5aa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Senior Azure Integration Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Moffitt Cancer Center</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a407a20c56f80680</t>
+          <t>https://www.indeed.com/viewjob?jk=d2fc45b22c56ab74</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FinOps Engineer (contract)</t>
+          <t>Sr. Software Engineer - AI Platforms and Automation</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Intelligent Medical Objects</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, ECS, RDS, Azure, GCP, Scala</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, PostgreSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba947e467674b693</t>
+          <t>https://www.indeed.com/viewjob?jk=60174baa1f0aad14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI Platforms and Automation</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Intelligent Medical Objects</t>
+          <t>Berkley</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, PostgreSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, dbt, MLflow</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60174baa1f0aad14</t>
+          <t>https://www.indeed.com/viewjob?jk=7656191539f10c8f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Berkley</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,77 +1116,77 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, dbt, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7656191539f10c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=9690379ea46f2be7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GE Appliances</t>
+          <t>Microtek Learning</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Silver Spring, MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, IAM, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f488fb42bdd9a3e5</t>
+          <t>https://www.indeed.com/viewjob?jk=35646364ed8f5219</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Moderna</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9690379ea46f2be7</t>
+          <t>https://www.indeed.com/viewjob?jk=d9727f7b8e7ba49f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Airflow (West Coast)</t>
+          <t>Technical Solution Architect - Salesforce Service Cloud</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>IT Shoulders, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563d41613641e2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=6285bc228bba1070</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JBoss Apache Fuse Engineer with Healthcare (RCM)</t>
+          <t>Solutions Architect (RICHMOND, VA, US, 23219)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Dominion Energy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdef99a180f7357d</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe9bd2b5131f29d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
+          <t>Artificial Intelligence Senior Data Scientist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f9fcd187c753bef</t>
+          <t>https://www.indeed.com/viewjob?jk=4a48e7242a74c765</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DevOps Engineer III — Cloud Automation &amp; Orchestration</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>Ideas2IT Technology Services</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tennyson, IN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=751a33e38e145115</t>
+          <t>https://www.indeed.com/viewjob?jk=3c514f50b938a8dc</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Full Stack Engineer, Data Services</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Moderna</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, ELT, MLflow</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9727f7b8e7ba49f</t>
+          <t>https://www.indeed.com/viewjob?jk=adcff14ee1b8e664</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Technical Solution Architect - Salesforce Service Cloud</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IT Shoulders, Inc.</t>
+          <t>Fieldwire</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Scala, DynamoDB, Data Modeling, ETL</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6285bc228bba1070</t>
+          <t>https://www.indeed.com/viewjob?jk=52528f466514c758</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Solutions Architect (RICHMOND, VA, US, 23219)</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Star Schema, Snowflake Schema</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe9bd2b5131f29d</t>
+          <t>https://www.indeed.com/viewjob?jk=5df64a9e9d059759</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Senior Data Scientist</t>
+          <t>Data Engineer- BI Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>Diversified Gas &amp; Oil</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a48e7242a74c765</t>
+          <t>https://www.indeed.com/viewjob?jk=d9cd4d53bb42fc00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Data Services</t>
+          <t>Sr Engineer, Software Engineer - Angular and Java</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcff14ee1b8e664</t>
+          <t>https://www.indeed.com/viewjob?jk=6dffa9c2d3180f00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Full-Stack Software Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ideas2IT Technology Services</t>
+          <t>iHeartMedia</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tennyson, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c514f50b938a8dc</t>
+          <t>https://www.indeed.com/viewjob?jk=30ce4ef971ec1d26</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Application Solutions Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fieldwire</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,29 +1571,29 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52528f466514c758</t>
+          <t>https://www.indeed.com/viewjob?jk=510eace270c01417</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Knowledge Graph Engineer/Semantic Web Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5df64a9e9d059759</t>
+          <t>https://www.indeed.com/viewjob?jk=f1326954160b9d00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer- BI Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Diversified Gas &amp; Oil</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9cd4d53bb42fc00</t>
+          <t>https://www.indeed.com/viewjob?jk=e9074111e1ca6eb3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Cloud Ops Engineer I - SRE</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CaseWorthy</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, GCP, Scala, Azure Cosmos DB, GitHub Actions, Azure DevOps, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d69f297c014e4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=7481c6f102626c6e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Application Solutions Architect</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>NextAmp LLC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,42 +1711,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>ECS, RDS, Snowflake, Oracle, SQL Server, Dimensional Modeling, Kimball, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=510eace270c01417</t>
+          <t>https://www.indeed.com/viewjob?jk=112573c8edf11915</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Knowledge Graph Engineer/Semantic Web Engineer</t>
+          <t>Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CONNEXUS CREDIT UNION</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,137 +1756,137 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1326954160b9d00</t>
+          <t>https://www.indeed.com/viewjob?jk=17489ce3b83eeabe</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9074111e1ca6eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=f722c5b892610593</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Business Analytics</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7481c6f102626c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=33816acdbf998550</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Development Engineer I - ArcGIS Enterprise</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Biztec Global</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b08010c09c91435</t>
+          <t>https://www.indeed.com/viewjob?jk=f1dd7af4bac5667f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>API/Microservices/AWS Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NextAmp LLC</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ECS, RDS, Snowflake, Oracle, SQL Server, Dimensional Modeling, Kimball, Star Schema, ETL, ELT</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=112573c8edf11915</t>
+          <t>https://www.indeed.com/viewjob?jk=d840931b85553d6b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CONNEXUS CREDIT UNION</t>
+          <t>Intuitive (Intuitive Surgical)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, ECS, RDS, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17489ce3b83eeabe</t>
+          <t>https://www.indeed.com/viewjob?jk=f24000cfeb877020</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,29 +1956,29 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f722c5b892610593</t>
+          <t>https://www.indeed.com/viewjob?jk=decf563d2df9d00c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data &amp; Analytics Platform (Snowflake/dbt)</t>
+          <t>Forward Deployed Engineer - AI SOC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt, Power BI, Tableau, DataOps</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f401900b912197cd</t>
+          <t>https://www.indeed.com/viewjob?jk=29fa83f558965646</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>Senior AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33816acdbf998550</t>
+          <t>https://www.indeed.com/viewjob?jk=0c44bbcac30a87c2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,77 +2061,77 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, MongoDB, Azure Cosmos DB, NoSQL, Data Modeling</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e899285a709ae99</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc37b1c10548573</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Quality and Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Biztec Global</t>
+          <t>Mercedes-Benz Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Vance, AL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1dd7af4bac5667f</t>
+          <t>https://www.indeed.com/viewjob?jk=3a36a0ff08797a70</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>API/Microservices/AWS Software Engineer - Remote</t>
+          <t>Senior Software Engineer, Coding</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,89 +2141,89 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d840931b85553d6b</t>
+          <t>https://www.indeed.com/viewjob?jk=f8090825b16fc51e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Senior Software Engineer, Data &amp; AI Platform</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Omada Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, NoSQL, ELT, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decf563d2df9d00c</t>
+          <t>https://www.indeed.com/viewjob?jk=94f84eddf97cd2cd</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Advanced Software Engineer- Full Stack Cloud Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Mass General Brigham</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78950b770ed7417f</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a26b0635f31911</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - AI SOC</t>
+          <t>Senior DevOps/MLOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Leverege</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2232,46 +2232,46 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fa83f558965646</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2c5ef617a021a1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Engineer</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c44bbcac30a87c2</t>
+          <t>https://www.indeed.com/viewjob?jk=be21268d9d981efd</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Engineer</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc37b1c10548573</t>
+          <t>https://www.indeed.com/viewjob?jk=f756de42016efc57</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mass General Brigham</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a26b0635f31911</t>
+          <t>https://www.indeed.com/viewjob?jk=abc756e24b7ebb78</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior DevOps/MLOps Engineer</t>
+          <t>Senior Snowflake Data Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Leverege</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, S3, RDS, Scala, Snowflake, DynamoDB, ELT, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2c5ef617a021a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a8050d86dd2bf8</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Azure Cloud Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>iHealth Innovative Solutions</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be21268d9d981efd</t>
+          <t>https://www.indeed.com/viewjob?jk=ed2e1c4a44c21b22</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Senior Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Bazz Houston International Manufacturing Solutions</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Garden Grove, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Oracle, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f756de42016efc57</t>
+          <t>https://www.indeed.com/viewjob?jk=5348150d7c9589e6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, ECS, RDS, Kafka, MySQL, MongoDB, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abc756e24b7ebb78</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dcbaf4daad4fc7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Platform Engineer (Hybrid)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>ThesisGrid</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,42 +2516,42 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, Snowflake, DynamoDB, ELT, Splunk, MLflow</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a8050d86dd2bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=d06761e86ca4aeca</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Quality and Data Engineer</t>
+          <t>Senior Software Engineer – Product</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>Re:Build Manufacturing</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Vance, AL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,207 +2561,207 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a36a0ff08797a70</t>
+          <t>https://www.indeed.com/viewjob?jk=61d08f5c56b39289</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Biztec Global</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36c700922532ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=34d1cfa7ddeeb193</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Azure Platform Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
+          <t>AWS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d19f755ee8489a</t>
+          <t>https://www.indeed.com/viewjob?jk=b121c03b7571c591</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWS Full Stack Developer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>Datadrive</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, Scala, DynamoDB</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Tableau, DataOps, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e284c3a4db13c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f20a50010d3a4e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ThesisGrid</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, DataOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d06761e86ca4aeca</t>
+          <t>https://www.indeed.com/viewjob?jk=0ebbf24573d559b5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Technical Architect - Enterprise Data</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Arista Networks</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf57c7d8b4b2d9e4</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e22338b7c0517c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Semantic Web Engineer or knowledge graph Engineer</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MagicForce</t>
+          <t>Avid Technology</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps, Terraform, Jenkins</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42f448146cc2551</t>
+          <t>https://www.indeed.com/viewjob?jk=42278e3835861af7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Senior UX Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Biztec Global</t>
+          <t>Charles River Analytics</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d1cfa7ddeeb193</t>
+          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Specialist, Software Engineer - Test Automation Developer (Ruby &amp; Playwright)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b121c03b7571c591</t>
+          <t>https://www.indeed.com/viewjob?jk=f00ee1189eddb9b1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Performance Engineer, Information technology</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Datadrive</t>
+          <t>ServiceLink</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Tableau, DataOps, GitHub Actions, Terraform, Airflow</t>
+          <t>API Gateway, RDS, Azure, Event Hubs, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, AKS</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f20a50010d3a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=f3af50fd888d2a26</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Product Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, DataOps</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ebbf24573d559b5</t>
+          <t>https://www.indeed.com/viewjob?jk=eeb8dc7b4cca4c33</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Product</t>
+          <t>AWS Devops - AOM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Re:Build Manufacturing</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Terraform</t>
+          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d08f5c56b39289</t>
+          <t>https://www.indeed.com/viewjob?jk=fe4c170529e0e9c9</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AWS Devops - AOM</t>
+          <t>Senior AWS Software Engineer (Integrations Team)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>City IT</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Marshfield, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe4c170529e0e9c9</t>
+          <t>https://www.indeed.com/viewjob?jk=4a82bf3693f26a75</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Marshfield, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a82bf3693f26a75</t>
+          <t>https://www.indeed.com/viewjob?jk=948d5244cfe1a3f8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior AWS Software Engineer (Integrations Team)</t>
+          <t>Business Intelligence Analyst I - REMOTE</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>City IT</t>
+          <t>Net Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=948d5244cfe1a3f8</t>
+          <t>https://www.indeed.com/viewjob?jk=2050bd296e3aa9f7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Full Stack | AI Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Avid Technology</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42278e3835861af7</t>
+          <t>https://www.indeed.com/viewjob?jk=80c4b497c4690c21</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer</t>
+          <t>Senior Development Operations Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>TTX</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
+          <t>https://www.indeed.com/viewjob?jk=730302ab09184768</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Specialist, Software Engineer - Test Automation Developer (Ruby &amp; Playwright)</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>VINMAR INTERNATIONAL</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins, Git</t>
+          <t>AWS, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3155,356 +3155,6 @@
         </is>
       </c>
       <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f00ee1189eddb9b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Performance Engineer, Information technology</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>ServiceLink</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Azure, Event Hubs, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, AKS</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f3af50fd888d2a26</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>VetsEZ</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb8dc7b4cca4c33</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>VetsEZ</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a7bee4a1e548e177</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>VetsEZ</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a54ac0922147b15</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Business Intelligence Analyst I - REMOTE</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Net Health</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2050bd296e3aa9f7</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Senior Development Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>TTX</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git, Azure Monitor, Python</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=730302ab09184768</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3e7fd121bc0e2325</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f41d2b8270473c0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a6494cda8c81441</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Forward Deployed Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>VINMAR INTERNATIONAL</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=43aa1a5e37a0ff4a</t>
         </is>

--- a/results/job_matches_2026-07-15.xlsx
+++ b/results/job_matches_2026-07-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,47 +538,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Azure Data -AI -Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>AEM Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Hadoop</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c9310d05771935</t>
+          <t>https://www.indeed.com/viewjob?jk=cb427fa873ed5fed</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer Remote - US • Remote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AEM Corporation</t>
+          <t>Daxko</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -591,24 +591,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Athena, SQS, SNS, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb427fa873ed5fed</t>
+          <t>https://www.indeed.com/viewjob?jk=d212feaf575e2588</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Remote - US • Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d212feaf575e2588</t>
+          <t>https://www.indeed.com/viewjob?jk=419f9c53a083aba9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Daxko</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Athena, SQS, SNS, RDS, Databricks, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=419f9c53a083aba9</t>
+          <t>https://www.indeed.com/viewjob?jk=a77df08519b290c1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Axiomatic AI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, GCP, Hadoop</t>
+          <t>AWS, API Gateway, RDS, Azure, Photon, GCP, Vertex AI, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77df08519b290c1</t>
+          <t>https://www.indeed.com/viewjob?jk=675661d633a7ce19</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Platform Engineer (Data 360)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Axiomatic AI</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Photon, GCP, Vertex AI, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Google Cloud Platform, Vertex AI, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675661d633a7ce19</t>
+          <t>https://www.indeed.com/viewjob?jk=25f44870043020f2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Data 360)</t>
+          <t>Senior Data Scientist - Artificial Intelligence</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Google Cloud Platform, Vertex AI, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f44870043020f2</t>
+          <t>https://www.indeed.com/viewjob?jk=7cf8977f54a3cd6f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Artificial Intelligence</t>
+          <t>Software Engineer III - C# / Java</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cf8977f54a3cd6f</t>
+          <t>https://www.indeed.com/viewjob?jk=bd35c029ba02435f</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Knowledge Graph Engineer/Semantic Web Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1326954160b9d00</t>
+          <t>https://www.indeed.com/viewjob?jk=e9074111e1ca6eb3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Knowledge Graph Engineer/Semantic Web Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9074111e1ca6eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=f1326954160b9d00</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NextAmp LLC</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ECS, RDS, Snowflake, Oracle, SQL Server, Dimensional Modeling, Kimball, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=112573c8edf11915</t>
+          <t>https://www.indeed.com/viewjob?jk=788999513395c430</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Business Intelligence Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CONNEXUS CREDIT UNION</t>
+          <t>NextAmp LLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>ECS, RDS, Snowflake, Oracle, SQL Server, Dimensional Modeling, Kimball, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17489ce3b83eeabe</t>
+          <t>https://www.indeed.com/viewjob?jk=112573c8edf11915</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Ops Engineer</t>
+          <t>Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Granite Telecommunications</t>
+          <t>CONNEXUS CREDIT UNION</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f722c5b892610593</t>
+          <t>https://www.indeed.com/viewjob?jk=17489ce3b83eeabe</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer - Business Analytics</t>
+          <t>Senior Cloud Data Ops Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Granite Telecommunications</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Oracle, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33816acdbf998550</t>
+          <t>https://www.indeed.com/viewjob?jk=f722c5b892610593</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Biztec Global</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1dd7af4bac5667f</t>
+          <t>https://www.indeed.com/viewjob?jk=70b73d6d3922b6ec</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>API/Microservices/AWS Software Engineer - Remote</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Varsity Spirit</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Oracle, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d840931b85553d6b</t>
+          <t>https://www.indeed.com/viewjob?jk=6bbf57b26961dcb5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Intuitive (Intuitive Surgical)</t>
+          <t>LINEVISION</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Athena, SQS, RDS, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f24000cfeb877020</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc506bd6bbd7df1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
+          <t>Data Engineer - Business Analytics</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>WSSC Water</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Laurel, MD, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decf563d2df9d00c</t>
+          <t>https://www.indeed.com/viewjob?jk=33816acdbf998550</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - AI SOC</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Biztec Global</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fa83f558965646</t>
+          <t>https://www.indeed.com/viewjob?jk=f1dd7af4bac5667f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Engineer</t>
+          <t>API/Microservices/AWS Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c44bbcac30a87c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d840931b85553d6b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Engineer</t>
+          <t>Advanced Metering Infrastructure (AMI) Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fiddler AI</t>
+          <t>WSSC Water</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Laurel, MD, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc37b1c10548573</t>
+          <t>https://www.indeed.com/viewjob?jk=decf563d2df9d00c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Quality and Data Engineer</t>
+          <t>Forward Deployed Engineer - AI SOC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Vance, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,102 +2106,102 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a36a0ff08797a70</t>
+          <t>https://www.indeed.com/viewjob?jk=29fa83f558965646</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Coding</t>
+          <t>Senior AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8090825b16fc51e</t>
+          <t>https://www.indeed.com/viewjob?jk=0c44bbcac30a87c2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data &amp; AI Platform</t>
+          <t>Senior AI Solutions Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Omada Health</t>
+          <t>Fiddler AI</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, NoSQL, ELT, MLflow, CI/CD</t>
+          <t>AWS, Kinesis, S3, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f84eddf97cd2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc37b1c10548573</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mass General Brigham</t>
+          <t>Intuitive (Intuitive Surgical)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
+          <t>AWS, Lambda, ECS, RDS, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a26b0635f31911</t>
+          <t>https://www.indeed.com/viewjob?jk=f24000cfeb877020</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior DevOps/MLOps Engineer</t>
+          <t>Sr. Software Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Leverege</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, HBase, Spark, Scala, Kafka, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2c5ef617a021a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d8a80a61bba60366</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Senior Software Engineer, Coding</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be21268d9d981efd</t>
+          <t>https://www.indeed.com/viewjob?jk=f8090825b16fc51e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (DBT)</t>
+          <t>Senior Software Engineer, Data &amp; AI Platform</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Omada Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, NoSQL, ELT, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f756de42016efc57</t>
+          <t>https://www.indeed.com/viewjob?jk=94f84eddf97cd2cd</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Gulfstream Aerospace</t>
+          <t>Mass General Brigham</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Savannah, GA, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abc756e24b7ebb78</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a26b0635f31911</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Snowflake Data Platform Engineer (Hybrid)</t>
+          <t>Senior DevOps/MLOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>Leverege</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, Snowflake, DynamoDB, ELT, Splunk, MLflow</t>
+          <t>AWS, IAM, Azure, GCP, Scala, PostgreSQL, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a8050d86dd2bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2c5ef617a021a1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Azure Cloud Architect</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>iHealth Innovative Solutions</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed2e1c4a44c21b22</t>
+          <t>https://www.indeed.com/viewjob?jk=be21268d9d981efd</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Quality Assurance Engineer</t>
+          <t>Senior Data Engineer (DBT)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bazz Houston International Manufacturing Solutions</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Garden Grove, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Oracle, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, Dimensional Modeling, ELT, dbt, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5348150d7c9589e6</t>
+          <t>https://www.indeed.com/viewjob?jk=f756de42016efc57</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Reporting Developer III - Cloud Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Gulfstream Aerospace</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Savannah, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Kafka, MySQL, MongoDB, Data Modeling, ETL, dbt</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5dcbaf4daad4fc7</t>
+          <t>https://www.indeed.com/viewjob?jk=abc756e24b7ebb78</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Snowflake Data Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ThesisGrid</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,77 +2516,77 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, S3, RDS, Scala, Snowflake, DynamoDB, ELT, Splunk, MLflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d06761e86ca4aeca</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a8050d86dd2bf8</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Product</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Re:Build Manufacturing</t>
+          <t>Vacatia, Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61d08f5c56b39289</t>
+          <t>https://www.indeed.com/viewjob?jk=808d72606614c9b0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Azure Cloud Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Biztec Global</t>
+          <t>iHealth Innovative Solutions</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d1cfa7ddeeb193</t>
+          <t>https://www.indeed.com/viewjob?jk=ed2e1c4a44c21b22</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Bazz Houston International Manufacturing Solutions</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Garden Grove, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>RDS, Azure, Oracle, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,94 +2631,94 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b121c03b7571c591</t>
+          <t>https://www.indeed.com/viewjob?jk=5348150d7c9589e6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Datadrive</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Tableau, DataOps, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, Kinesis, ECS, RDS, Kafka, MySQL, MongoDB, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f20a50010d3a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=e5dcbaf4daad4fc7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>ThesisGrid</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, DataOps</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ebbf24573d559b5</t>
+          <t>https://www.indeed.com/viewjob?jk=d06761e86ca4aeca</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Technical Architect - Enterprise Data</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>Biztec Global</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e22338b7c0517c</t>
+          <t>https://www.indeed.com/viewjob?jk=34d1cfa7ddeeb193</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Avid Technology</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42278e3835861af7</t>
+          <t>https://www.indeed.com/viewjob?jk=b121c03b7571c591</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>Datadrive</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Tableau, DataOps, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f20a50010d3a4e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Specialist, Software Engineer - Test Automation Developer (Ruby &amp; Playwright)</t>
+          <t>CCaaS GCP Product Owner</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Betsol</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins, Git</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Kafka, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f00ee1189eddb9b1</t>
+          <t>https://www.indeed.com/viewjob?jk=e12026ecbd107234</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Performance Engineer, Information technology</t>
+          <t>Expert Data Scientist</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ServiceLink</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,29 +2866,29 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Event Hubs, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, MLOps, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3af50fd888d2a26</t>
+          <t>https://www.indeed.com/viewjob?jk=9492d4954650eb7f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Product Engineer (Remote Opportunity)</t>
+          <t>Technical Architect - Enterprise Data</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>Arista Networks</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb8dc7b4cca4c33</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e22338b7c0517c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AWS Devops - AOM</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Avid Technology</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe4c170529e0e9c9</t>
+          <t>https://www.indeed.com/viewjob?jk=42278e3835861af7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior AWS Software Engineer (Integrations Team)</t>
+          <t>Senior UX Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>City IT</t>
+          <t>Charles River Analytics</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Marshfield, MA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a82bf3693f26a75</t>
+          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior AWS Software Engineer (Integrations Team)</t>
+          <t>Specialist, Software Engineer - Test Automation Developer (Ruby &amp; Playwright)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>City IT</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=948d5244cfe1a3f8</t>
+          <t>https://www.indeed.com/viewjob?jk=f00ee1189eddb9b1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst I - REMOTE</t>
+          <t>Performance Engineer, Information technology</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Net Health</t>
+          <t>ServiceLink</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, dbt, Power BI, Tableau</t>
+          <t>API Gateway, RDS, Azure, Event Hubs, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, AKS</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2050bd296e3aa9f7</t>
+          <t>https://www.indeed.com/viewjob?jk=f3af50fd888d2a26</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full Stack | AI Developer</t>
+          <t>AWS Devops - AOM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c4b497c4690c21</t>
+          <t>https://www.indeed.com/viewjob?jk=fe4c170529e0e9c9</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Development Operations Engineer</t>
+          <t>Senior AWS Software Engineer (Integrations Team)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>City IT</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Marshfield, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, Git, Azure Monitor, Python</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730302ab09184768</t>
+          <t>https://www.indeed.com/viewjob?jk=4a82bf3693f26a75</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior AWS Software Engineer (Integrations Team)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>VINMAR INTERNATIONAL</t>
+          <t>City IT</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,15 +3146,120 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=948d5244cfe1a3f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Business Intelligence Analyst I - REMOTE</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Net Health</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2050bd296e3aa9f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Full Stack | AI Developer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80c4b497c4690c21</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>VINMAR INTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>AWS, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, Docker</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=43aa1a5e37a0ff4a</t>
         </is>

--- a/results/job_matches_2026-07-15.xlsx
+++ b/results/job_matches_2026-07-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Senior Data Scientist</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>Ideas2IT Technology Services</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tennyson, IN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a48e7242a74c765</t>
+          <t>https://www.indeed.com/viewjob?jk=3c514f50b938a8dc</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Full Stack Engineer, Data Services</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ideas2IT Technology Services</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tennyson, IN, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c514f50b938a8dc</t>
+          <t>https://www.indeed.com/viewjob?jk=adcff14ee1b8e664</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Data Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Fieldwire</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Snowflake, Data Modeling, Dimensional Modeling, dbt, CI/CD, Docker</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adcff14ee1b8e664</t>
+          <t>https://www.indeed.com/viewjob?jk=52528f466514c758</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fieldwire</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52528f466514c758</t>
+          <t>https://www.indeed.com/viewjob?jk=5df64a9e9d059759</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Data Engineer- BI Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Diversified Gas &amp; Oil</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5df64a9e9d059759</t>
+          <t>https://www.indeed.com/viewjob?jk=d9cd4d53bb42fc00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer- BI Developer</t>
+          <t>Sr. Software Engineer - ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Diversified Gas &amp; Oil</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, S3, SQS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, Maven</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9cd4d53bb42fc00</t>
+          <t>https://www.indeed.com/viewjob?jk=239b32e292b68704</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RBC</t>
+          <t>LINEVISION</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, NoSQL, ETL, Power BI, Tableau</t>
+          <t>AWS, Glue, Lambda, Athena, SQS, RDS, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70b73d6d3922b6ec</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc506bd6bbd7df1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Data engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Varsity Spirit</t>
+          <t>Biztec Global</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Oracle, PostgreSQL, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bbf57b26961dcb5</t>
+          <t>https://www.indeed.com/viewjob?jk=f1dd7af4bac5667f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LINEVISION</t>
+          <t>Varsity Spirit</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, SQS, RDS, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Oracle, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc506bd6bbd7df1</t>
+          <t>https://www.indeed.com/viewjob?jk=6bbf57b26961dcb5</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data engineer</t>
+          <t>API/Microservices/AWS Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Biztec Global</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1dd7af4bac5667f</t>
+          <t>https://www.indeed.com/viewjob?jk=d840931b85553d6b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>API/Microservices/AWS Software Engineer - Remote</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d840931b85553d6b</t>
+          <t>https://www.indeed.com/viewjob?jk=70b73d6d3922b6ec</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Biztec Global</t>
+          <t>Münchener Rückversicherungs-Gesellschaft</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ELT, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d1cfa7ddeeb193</t>
+          <t>https://www.indeed.com/viewjob?jk=eae68457635010f5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Biztec Global</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b121c03b7571c591</t>
+          <t>https://www.indeed.com/viewjob?jk=34d1cfa7ddeeb193</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Datadrive</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Tableau, DataOps, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5f20a50010d3a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=b121c03b7571c591</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CCaaS GCP Product Owner</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Betsol</t>
+          <t>Datadrive</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,29 +2831,29 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Kafka, Power BI, Tableau</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Tableau, DataOps, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e12026ecbd107234</t>
+          <t>https://www.indeed.com/viewjob?jk=f5f20a50010d3a4e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Expert Data Scientist</t>
+          <t>AWS Devops - AOM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, NoSQL, MLOps, Git</t>
+          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9492d4954650eb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=fe4c170529e0e9c9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Technical Architect - Enterprise Data</t>
+          <t>Senior AWS Software Engineer (Integrations Team)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>City IT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Marshfield, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e22338b7c0517c</t>
+          <t>https://www.indeed.com/viewjob?jk=4a82bf3693f26a75</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Senior AWS Software Engineer (Integrations Team)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Avid Technology</t>
+          <t>City IT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42278e3835861af7</t>
+          <t>https://www.indeed.com/viewjob?jk=948d5244cfe1a3f8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer</t>
+          <t>CCaaS GCP Product Owner</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>Betsol</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Kafka, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
+          <t>https://www.indeed.com/viewjob?jk=e12026ecbd107234</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Specialist, Software Engineer - Test Automation Developer (Ruby &amp; Playwright)</t>
+          <t>Technical Architect - Enterprise Data</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Arista Networks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f00ee1189eddb9b1</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e22338b7c0517c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Performance Engineer, Information technology</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ServiceLink</t>
+          <t>Avid Technology</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Event Hubs, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, AKS</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3af50fd888d2a26</t>
+          <t>https://www.indeed.com/viewjob?jk=42278e3835861af7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AWS Devops - AOM</t>
+          <t>Senior UX Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Charles River Analytics</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe4c170529e0e9c9</t>
+          <t>https://www.indeed.com/viewjob?jk=e62e78236a52a218</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior AWS Software Engineer (Integrations Team)</t>
+          <t>Specialist, Software Engineer - Test Automation Developer (Ruby &amp; Playwright)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>City IT</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Marshfield, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a82bf3693f26a75</t>
+          <t>https://www.indeed.com/viewjob?jk=f00ee1189eddb9b1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior AWS Software Engineer (Integrations Team)</t>
+          <t>Business Intelligence Analyst I - REMOTE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>City IT</t>
+          <t>Net Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=948d5244cfe1a3f8</t>
+          <t>https://www.indeed.com/viewjob?jk=2050bd296e3aa9f7</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst I - REMOTE</t>
+          <t>Full Stack | AI Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Net Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,77 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2050bd296e3aa9f7</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Full Stack | AI Developer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=80c4b497c4690c21</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Forward Deployed Engineer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>VINMAR INTERNATIONAL</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=43aa1a5e37a0ff4a</t>
         </is>
       </c>
     </row>
